--- a/创新支撑系统-功能点走查记录.xlsx
+++ b/创新支撑系统-功能点走查记录.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WPS Office\12.1.0.28505\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00 云上江西\03 赣政通\创新支撑平台\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="465">
   <si>
     <t>序号</t>
   </si>
@@ -256,24 +256,6 @@
     <t>接口示例管理</t>
   </si>
   <si>
-    <t>接口示例新增</t>
-  </si>
-  <si>
-    <t>对接口示例新增进行配置管理操作</t>
-  </si>
-  <si>
-    <t>接口示例修改</t>
-  </si>
-  <si>
-    <t>对接口示例修改进行配置管理操作</t>
-  </si>
-  <si>
-    <t>接口示例删除</t>
-  </si>
-  <si>
-    <t>对接口示例删除进行配置管理操作</t>
-  </si>
-  <si>
     <t>接口示例批量删除</t>
   </si>
   <si>
@@ -286,12 +268,6 @@
     <t>对接口示例查询字段排序进行配置管理操作</t>
   </si>
   <si>
-    <t>接口示例查看</t>
-  </si>
-  <si>
-    <t>对接口示例查看进行配置管理操作</t>
-  </si>
-  <si>
     <t>接口示例查询</t>
   </si>
   <si>
@@ -301,24 +277,6 @@
     <t>接口错误码管理</t>
   </si>
   <si>
-    <t>接口错误码新增</t>
-  </si>
-  <si>
-    <t>对接口错误码新增进行配置管理操作</t>
-  </si>
-  <si>
-    <t>接口错误码修改</t>
-  </si>
-  <si>
-    <t>对接口错误码修改进行配置管理操作</t>
-  </si>
-  <si>
-    <t>接口错误码删除</t>
-  </si>
-  <si>
-    <t>对接口错误码删除进行配置管理操作</t>
-  </si>
-  <si>
     <t>接口错误码批量删除</t>
   </si>
   <si>
@@ -331,12 +289,6 @@
     <t>对接口错误码查询字段排序进行配置管理操作</t>
   </si>
   <si>
-    <t>接口错误码查看</t>
-  </si>
-  <si>
-    <t>对接口错误码查看进行配置管理操作</t>
-  </si>
-  <si>
     <t>接口错误码查询</t>
   </si>
   <si>
@@ -418,6 +370,21 @@
     <t>对工单审批退回进行配置管理操作</t>
   </si>
   <si>
+    <t>帮助信息管理</t>
+  </si>
+  <si>
+    <t>帮助版本记录</t>
+  </si>
+  <si>
+    <t>对帮助版本记录进行配置管理操作</t>
+  </si>
+  <si>
+    <t>帮助文档目录移动</t>
+  </si>
+  <si>
+    <t>对帮助文档目录移动进行配置管理操作</t>
+  </si>
+  <si>
     <t>应用案例管理</t>
   </si>
   <si>
@@ -433,81 +400,12 @@
     <t>软件服务商入驻管理</t>
   </si>
   <si>
-    <t>入驻申请单查看</t>
-  </si>
-  <si>
-    <t>对入驻申请单查看进行配置管理操作</t>
-  </si>
-  <si>
-    <t>入驻申请单审核</t>
-  </si>
-  <si>
-    <t>对入驻申请单审核进行配置管理操作</t>
-  </si>
-  <si>
-    <t>申请服务商查询</t>
-  </si>
-  <si>
-    <t>对申请服务商查询进行配置管理操作</t>
-  </si>
-  <si>
     <t>申请服务商查询重置</t>
   </si>
   <si>
     <t>对申请服务商查询重置进行配置管理操作</t>
   </si>
   <si>
-    <t>入驻申请单状态分类</t>
-  </si>
-  <si>
-    <t>对入驻申请单状态分类进行配置管理操作</t>
-  </si>
-  <si>
-    <t>软件服务商登录管理</t>
-  </si>
-  <si>
-    <t>验证码配置新增</t>
-  </si>
-  <si>
-    <t>对验证码配置新增进行配置管理操作</t>
-  </si>
-  <si>
-    <t>验证码配置修改</t>
-  </si>
-  <si>
-    <t>对验证码配置修改进行配置管理操作</t>
-  </si>
-  <si>
-    <t>验证码配置删除</t>
-  </si>
-  <si>
-    <t>对验证码配置删除进行配置管理操作</t>
-  </si>
-  <si>
-    <t>验证码配置批量删除</t>
-  </si>
-  <si>
-    <t>对验证码配置批量删除进行配置管理操作</t>
-  </si>
-  <si>
-    <t>验证码配置查询排序</t>
-  </si>
-  <si>
-    <t>对验证码配置查询排序进行配置管理操作</t>
-  </si>
-  <si>
-    <t>验证码配置查看</t>
-  </si>
-  <si>
-    <t>对验证码配置查看进行配置管理操作</t>
-  </si>
-  <si>
-    <t>验证码配置查询</t>
-  </si>
-  <si>
-    <t>对验证码配置查询进行配置管理操作</t>
-  </si>
-  <si>
     <t>软件服务商管理</t>
   </si>
   <si>
@@ -760,12 +658,6 @@
     <t>对用户批量删除进行配置管理操作</t>
   </si>
   <si>
-    <t>用户机构关联批量删除</t>
-  </si>
-  <si>
-    <t>对用户机构关联批量删除进行配置管理操作</t>
-  </si>
-  <si>
     <t>用户拓展信息删除</t>
   </si>
   <si>
@@ -820,69 +712,6 @@
     <t>对用户职级关联查询字段排序进行配置管理操作</t>
   </si>
   <si>
-    <t>岗位管理</t>
-  </si>
-  <si>
-    <t>岗位信息新增</t>
-  </si>
-  <si>
-    <t>对岗位信息新增进行配置管理操作</t>
-  </si>
-  <si>
-    <t>岗位信息修改</t>
-  </si>
-  <si>
-    <t>对岗位信息修改进行配置管理操作</t>
-  </si>
-  <si>
-    <t>岗位信息删除</t>
-  </si>
-  <si>
-    <t>对岗位信息删除进行配置管理操作</t>
-  </si>
-  <si>
-    <t>岗位信息批量删除</t>
-  </si>
-  <si>
-    <t>对岗位信息批量删除进行配置管理操作</t>
-  </si>
-  <si>
-    <t>岗位信息查询字段排序</t>
-  </si>
-  <si>
-    <t>对岗位信息查询字段排序进行配置管理操作</t>
-  </si>
-  <si>
-    <t>岗位信息查看</t>
-  </si>
-  <si>
-    <t>对岗位信息查看进行配置管理操作</t>
-  </si>
-  <si>
-    <t>岗位信息查询</t>
-  </si>
-  <si>
-    <t>对岗位信息查询进行配置管理操作</t>
-  </si>
-  <si>
-    <t>职称管理</t>
-  </si>
-  <si>
-    <t>职称查询字段排序</t>
-  </si>
-  <si>
-    <t>对职称查询字段排序进行配置管理操作</t>
-  </si>
-  <si>
-    <t>职级管理</t>
-  </si>
-  <si>
-    <t>职级查询字段排序</t>
-  </si>
-  <si>
-    <t>对职级查询字段排序进行配置管理操作</t>
-  </si>
-  <si>
     <t>职务新增</t>
   </si>
   <si>
@@ -994,12 +823,6 @@
     <t>对操作日志配置查询字段排序进行配置管理操作</t>
   </si>
   <si>
-    <t>操作日志配置查看</t>
-  </si>
-  <si>
-    <t>对操作日志配置查看进行配置管理操作</t>
-  </si>
-  <si>
     <t>操作日志配置查询</t>
   </si>
   <si>
@@ -1054,12 +877,6 @@
     <t>对订阅日志配置查询字段排序进行配置管理操作</t>
   </si>
   <si>
-    <t>订阅日志配置查看</t>
-  </si>
-  <si>
-    <t>对订阅日志配置查看进行配置管理操作</t>
-  </si>
-  <si>
     <t>订阅日志配置查询</t>
   </si>
   <si>
@@ -1132,12 +949,6 @@
     <t>对全量推送日志配置查询字段排序进行配置管理操作</t>
   </si>
   <si>
-    <t>全量推送日志配置查看</t>
-  </si>
-  <si>
-    <t>对全量推送日志配置查看进行配置管理操作</t>
-  </si>
-  <si>
     <t>全量推送日志配置查询</t>
   </si>
   <si>
@@ -1364,30 +1175,6 @@
   </si>
   <si>
     <t>对工单评价新增进行配置管理操作</t>
-  </si>
-  <si>
-    <t>工单评价修改</t>
-  </si>
-  <si>
-    <t>对工单评价修改进行配置管理操作</t>
-  </si>
-  <si>
-    <t>工单评价删除</t>
-  </si>
-  <si>
-    <t>对工单评价删除进行配置管理操作</t>
-  </si>
-  <si>
-    <t>工单评价查询</t>
-  </si>
-  <si>
-    <t>对工单评价查询进行配置管理操作</t>
-  </si>
-  <si>
-    <t>工单评价参数设置</t>
-  </si>
-  <si>
-    <t>对工单评价参数设置进行配置管理操作</t>
   </si>
   <si>
     <t>办件中心</t>
@@ -1652,7 +1439,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1676,12 +1463,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FFC00000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2202,13 +1983,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2217,122 +2001,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2357,7 +2138,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3371,9 +3161,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" ht="49.7" spans="1:7">
+    <row r="22" ht="62.15" spans="1:7">
       <c r="A22" s="3">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
@@ -3394,9 +3184,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" ht="49.7" spans="1:7">
+    <row r="23" ht="62.15" spans="1:7">
       <c r="A23" s="3">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
@@ -3419,7 +3209,7 @@
     </row>
     <row r="24" ht="49.7" spans="1:7">
       <c r="A24" s="3">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>7</v>
@@ -3442,7 +3232,7 @@
     </row>
     <row r="25" ht="62.15" spans="1:7">
       <c r="A25" s="3">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
@@ -3454,18 +3244,18 @@
         <v>69</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" ht="62.15" spans="1:7">
       <c r="A26" s="3">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
@@ -3477,18 +3267,18 @@
         <v>69</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="49.7" spans="1:7">
       <c r="A27" s="3">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
@@ -3500,18 +3290,18 @@
         <v>69</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="49.7" spans="1:7">
       <c r="A28" s="3">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>7</v>
@@ -3520,21 +3310,21 @@
         <v>57</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="49.7" spans="1:7">
       <c r="A29" s="3">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
@@ -3543,21 +3333,21 @@
         <v>57</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="49.7" spans="1:7">
       <c r="A30" s="3">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>7</v>
@@ -3566,21 +3356,21 @@
         <v>57</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" ht="49.7" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" ht="62.15" spans="1:7">
       <c r="A31" s="3">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
@@ -3589,21 +3379,21 @@
         <v>57</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" ht="62.15" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" ht="49.7" spans="1:7">
       <c r="A32" s="3">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>7</v>
@@ -3612,21 +3402,21 @@
         <v>57</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" ht="62.15" spans="1:7">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" ht="49.7" spans="1:7">
       <c r="A33" s="3">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
@@ -3635,21 +3425,21 @@
         <v>57</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" ht="49.7" spans="1:7">
       <c r="A34" s="3">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>7</v>
@@ -3658,21 +3448,21 @@
         <v>57</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" ht="49.7" spans="1:7">
       <c r="A35" s="3">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
@@ -3681,21 +3471,21 @@
         <v>57</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" ht="49.7" spans="1:7">
       <c r="A36" s="3">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>7</v>
@@ -3704,7 +3494,7 @@
         <v>57</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>26</v>
@@ -3718,7 +3508,7 @@
     </row>
     <row r="37" ht="49.7" spans="1:7">
       <c r="A37" s="3">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>7</v>
@@ -3727,7 +3517,7 @@
         <v>57</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>26</v>
@@ -3741,7 +3531,7 @@
     </row>
     <row r="38" ht="49.7" spans="1:7">
       <c r="A38" s="3">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>7</v>
@@ -3750,7 +3540,7 @@
         <v>57</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>26</v>
@@ -3762,9 +3552,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" ht="62.15" spans="1:7">
+    <row r="39" ht="49.7" spans="1:7">
       <c r="A39" s="3">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
@@ -3773,7 +3563,7 @@
         <v>57</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>26</v>
@@ -3787,7 +3577,7 @@
     </row>
     <row r="40" ht="49.7" spans="1:7">
       <c r="A40" s="3">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
@@ -3796,21 +3586,21 @@
         <v>57</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>112</v>
+      <c r="F40" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" ht="49.7" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" ht="62.15" spans="1:7">
       <c r="A41" s="3">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
@@ -3819,21 +3609,21 @@
         <v>57</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" ht="49.7" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" ht="62.15" spans="1:7">
       <c r="A42" s="3">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>7</v>
@@ -3842,585 +3632,585 @@
         <v>57</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" ht="49.7" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" ht="62.15" spans="1:7">
       <c r="A43" s="3">
-        <v>553</v>
+        <v>601</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="44" ht="49.7" spans="1:7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" ht="74.55" spans="1:7">
       <c r="A44" s="3">
-        <v>554</v>
+        <v>621</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" ht="74.55" spans="1:7">
+      <c r="A45" s="3">
+        <v>622</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" ht="49.7" spans="1:7">
-      <c r="A45" s="3">
-        <v>555</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="D45" s="4" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" ht="49.7" spans="1:7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" ht="74.55" spans="1:7">
       <c r="A46" s="3">
-        <v>556</v>
+        <v>623</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" ht="74.55" spans="1:7">
+      <c r="A47" s="3">
+        <v>624</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="47" ht="49.7" spans="1:7">
-      <c r="A47" s="3">
-        <v>557</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" ht="62.15" spans="1:7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" ht="87" spans="1:7">
       <c r="A48" s="3">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" ht="49.7" spans="1:7">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" ht="62.15" spans="1:7">
       <c r="A49" s="3">
-        <v>598</v>
+        <v>638</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" ht="49.7" spans="1:7">
       <c r="A50" s="3">
-        <v>599</v>
+        <v>639</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" ht="49.7" spans="1:7">
       <c r="A51" s="3">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" ht="62.15" spans="1:7">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" ht="49.7" spans="1:7">
       <c r="A52" s="3">
-        <v>601</v>
+        <v>678</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="53" ht="62.15" spans="1:7">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" ht="49.7" spans="1:7">
       <c r="A53" s="3">
-        <v>602</v>
+        <v>679</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" ht="49.7" spans="1:7">
       <c r="A54" s="3">
-        <v>606</v>
+        <v>680</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="55" ht="49.7" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" ht="62.15" spans="1:7">
       <c r="A55" s="3">
-        <v>607</v>
+        <v>681</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="56" ht="49.7" spans="1:7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" ht="62.15" spans="1:7">
       <c r="A56" s="3">
-        <v>608</v>
+        <v>682</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="57" ht="62.15" spans="1:7">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" ht="49.7" spans="1:7">
       <c r="A57" s="3">
-        <v>609</v>
+        <v>683</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="58" ht="62.15" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" ht="49.7" spans="1:7">
       <c r="A58" s="3">
-        <v>610</v>
+        <v>684</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="59" ht="49.7" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" ht="62.15" spans="1:7">
       <c r="A59" s="3">
-        <v>611</v>
+        <v>685</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="60" ht="49.7" spans="1:7">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60" ht="62.15" spans="1:7">
       <c r="A60" s="3">
-        <v>612</v>
+        <v>686</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="61" ht="74.55" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" ht="62.15" spans="1:7">
       <c r="A61" s="3">
-        <v>621</v>
+        <v>687</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" ht="74.55" spans="1:7">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" ht="62.15" spans="1:7">
       <c r="A62" s="3">
-        <v>622</v>
+        <v>688</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" ht="74.55" spans="1:7">
       <c r="A63" s="3">
-        <v>623</v>
+        <v>689</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="64" ht="74.55" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" ht="62.15" spans="1:7">
       <c r="A64" s="3">
-        <v>624</v>
+        <v>690</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="65" ht="87" spans="1:7">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" ht="62.15" spans="1:7">
       <c r="A65" s="3">
-        <v>633</v>
+        <v>691</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="66" ht="62.15" spans="1:7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" ht="49.7" spans="1:7">
       <c r="A66" s="3">
-        <v>638</v>
+        <v>692</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" ht="49.7" spans="1:7">
       <c r="A67" s="3">
-        <v>639</v>
+        <v>693</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>172</v>
@@ -4431,19 +4221,19 @@
     </row>
     <row r="68" ht="49.7" spans="1:7">
       <c r="A68" s="3">
-        <v>640</v>
+        <v>694</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>174</v>
@@ -4452,9 +4242,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" ht="49.7" spans="1:7">
+    <row r="69" ht="62.15" spans="1:7">
       <c r="A69" s="3">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>7</v>
@@ -4466,7 +4256,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>176</v>
@@ -4475,9 +4265,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" ht="49.7" spans="1:7">
+    <row r="70" ht="62.15" spans="1:7">
       <c r="A70" s="3">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>7</v>
@@ -4489,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>178</v>
@@ -4500,7 +4290,7 @@
     </row>
     <row r="71" ht="49.7" spans="1:7">
       <c r="A71" s="3">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>7</v>
@@ -4512,7 +4302,7 @@
         <v>9</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>180</v>
@@ -4521,9 +4311,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" ht="62.15" spans="1:7">
+    <row r="72" ht="49.7" spans="1:7">
       <c r="A72" s="3">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>7</v>
@@ -4535,7 +4325,7 @@
         <v>9</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>182</v>
@@ -4546,7 +4336,7 @@
     </row>
     <row r="73" ht="62.15" spans="1:7">
       <c r="A73" s="3">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>7</v>
@@ -4558,18 +4348,18 @@
         <v>9</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="74" ht="49.7" spans="1:7">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" ht="62.15" spans="1:7">
       <c r="A74" s="3">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>7</v>
@@ -4581,18 +4371,18 @@
         <v>9</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="75" ht="49.7" spans="1:7">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" ht="62.15" spans="1:7">
       <c r="A75" s="3">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>7</v>
@@ -4604,18 +4394,18 @@
         <v>9</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" ht="62.15" spans="1:7">
       <c r="A76" s="3">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>7</v>
@@ -4627,18 +4417,18 @@
         <v>9</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="77" ht="62.15" spans="1:7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" ht="74.55" spans="1:7">
       <c r="A77" s="3">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>7</v>
@@ -4650,18 +4440,18 @@
         <v>9</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" ht="62.15" spans="1:7">
       <c r="A78" s="3">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>7</v>
@@ -4673,18 +4463,18 @@
         <v>9</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" ht="62.15" spans="1:7">
       <c r="A79" s="3">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>7</v>
@@ -4696,18 +4486,18 @@
         <v>9</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="80" ht="74.55" spans="1:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="80" ht="49.7" spans="1:7">
       <c r="A80" s="3">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>7</v>
@@ -4719,409 +4509,409 @@
         <v>9</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="81" ht="62.15" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" ht="49.7" spans="1:7">
       <c r="A81" s="3">
-        <v>690</v>
+        <v>749</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G81" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="82" ht="49.7" spans="1:7">
+      <c r="A82" s="3">
+        <v>761</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="82" ht="62.15" spans="1:7">
-      <c r="A82" s="3">
-        <v>691</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E82" s="4" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="83" ht="49.7" spans="1:7">
       <c r="A83" s="3">
-        <v>692</v>
+        <v>768</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F83" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G83" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G83" s="6" t="s">
+    </row>
+    <row r="84" ht="62.15" spans="1:7">
+      <c r="A84" s="3">
+        <v>787</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="84" ht="49.7" spans="1:7">
-      <c r="A84" s="3">
-        <v>693</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>206</v>
+      <c r="F84" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="85" ht="49.7" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="85" ht="62.15" spans="1:7">
       <c r="A85" s="3">
-        <v>694</v>
+        <v>788</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="86" ht="62.15" spans="1:7">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" ht="74.55" spans="1:7">
       <c r="A86" s="3">
-        <v>695</v>
+        <v>789</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" ht="62.15" spans="1:7">
       <c r="A87" s="3">
-        <v>696</v>
+        <v>797</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>212</v>
+        <v>205</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="88" ht="49.7" spans="1:7">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" ht="74.55" spans="1:7">
       <c r="A88" s="3">
-        <v>697</v>
+        <v>798</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="89" ht="49.7" spans="1:7">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" ht="62.15" spans="1:7">
       <c r="A89" s="3">
-        <v>698</v>
+        <v>804</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="90" ht="62.15" spans="1:7">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="90" ht="74.55" spans="1:7">
       <c r="A90" s="3">
-        <v>707</v>
+        <v>805</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" ht="62.15" spans="1:7">
       <c r="A91" s="3">
-        <v>708</v>
+        <v>811</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="92" ht="62.15" spans="1:7">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="92" ht="74.55" spans="1:7">
       <c r="A92" s="3">
-        <v>709</v>
+        <v>812</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="93" ht="62.15" spans="1:7">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="93" ht="49.7" spans="1:7">
       <c r="A93" s="3">
-        <v>710</v>
+        <v>851</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>225</v>
+        <v>20</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="94" ht="74.55" spans="1:7">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="94" ht="49.7" spans="1:7">
       <c r="A94" s="3">
-        <v>711</v>
+        <v>852</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>227</v>
+        <v>20</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="95" ht="62.15" spans="1:7">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="95" ht="49.7" spans="1:7">
       <c r="A95" s="3">
-        <v>712</v>
+        <v>853</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>229</v>
+        <v>20</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="96" ht="62.15" spans="1:7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96" ht="49.7" spans="1:7">
       <c r="A96" s="3">
-        <v>713</v>
+        <v>854</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>231</v>
+        <v>20</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" ht="49.7" spans="1:7">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="97" ht="62.15" spans="1:7">
       <c r="A97" s="3">
-        <v>714</v>
+        <v>855</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>233</v>
+        <v>20</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="98" ht="49.7" spans="1:7">
       <c r="A98" s="3">
-        <v>749</v>
+        <v>856</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>7</v>
@@ -5130,21 +4920,21 @@
         <v>19</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E98" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="G98" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="99" ht="49.7" spans="1:7">
       <c r="A99" s="3">
-        <v>761</v>
+        <v>857</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>7</v>
@@ -5153,21 +4943,21 @@
         <v>19</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E99" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G99" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="100" ht="49.7" spans="1:7">
       <c r="A100" s="3">
-        <v>768</v>
+        <v>858</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>7</v>
@@ -5176,21 +4966,21 @@
         <v>19</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>237</v>
+        <v>20</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="101" ht="62.15" spans="1:7">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" ht="49.7" spans="1:7">
       <c r="A101" s="3">
-        <v>781</v>
+        <v>859</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>7</v>
@@ -5199,12 +4989,12 @@
         <v>19</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F101" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" s="6" t="s">
         <v>242</v>
       </c>
       <c r="G101" s="6" t="s">
@@ -5213,640 +5003,640 @@
     </row>
     <row r="102" ht="62.15" spans="1:7">
       <c r="A102" s="3">
-        <v>787</v>
+        <v>1054</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>244</v>
+        <v>26</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" ht="62.15" spans="1:7">
       <c r="A103" s="3">
-        <v>788</v>
+        <v>1069</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>246</v>
+        <v>26</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="104" ht="74.55" spans="1:7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="104" ht="62.15" spans="1:7">
       <c r="A104" s="3">
-        <v>789</v>
+        <v>1243</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105" ht="62.15" spans="1:7">
       <c r="A105" s="3">
-        <v>797</v>
+        <v>1244</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="G105" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="106" ht="62.15" spans="1:7">
+      <c r="A106" s="3">
+        <v>1245</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="106" ht="74.55" spans="1:7">
-      <c r="A106" s="3">
-        <v>798</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="E106" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" ht="62.15" spans="1:7">
       <c r="A107" s="3">
-        <v>804</v>
+        <v>1246</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108" ht="74.55" spans="1:7">
       <c r="A108" s="3">
-        <v>805</v>
+        <v>1247</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" ht="62.15" spans="1:7">
       <c r="A109" s="3">
-        <v>811</v>
+        <v>1249</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="110" ht="74.55" spans="1:7">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="110" ht="49.7" spans="1:7">
       <c r="A110" s="3">
-        <v>812</v>
+        <v>1250</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" ht="49.7" spans="1:7">
       <c r="A111" s="3">
-        <v>826</v>
+        <v>1251</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>263</v>
+        <v>251</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" ht="49.7" spans="1:7">
       <c r="A112" s="3">
-        <v>827</v>
+        <v>1252</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="113" ht="49.7" spans="1:7">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" ht="62.15" spans="1:7">
       <c r="A113" s="3">
-        <v>828</v>
+        <v>1253</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" ht="62.15" spans="1:7">
       <c r="A114" s="3">
-        <v>829</v>
+        <v>1254</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="115" ht="62.15" spans="1:7">
       <c r="A115" s="3">
-        <v>830</v>
+        <v>1255</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="116" ht="49.7" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="116" ht="62.15" spans="1:7">
       <c r="A116" s="3">
-        <v>831</v>
+        <v>1256</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="117" ht="49.7" spans="1:7">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="117" ht="74.55" spans="1:7">
       <c r="A117" s="3">
-        <v>832</v>
+        <v>1257</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" ht="62.15" spans="1:7">
       <c r="A118" s="3">
-        <v>837</v>
+        <v>1259</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>278</v>
+        <v>252</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="119" ht="62.15" spans="1:7">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="119" ht="49.7" spans="1:7">
       <c r="A119" s="3">
-        <v>846</v>
+        <v>1260</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" ht="49.7" spans="1:7">
       <c r="A120" s="3">
-        <v>851</v>
+        <v>1261</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>21</v>
+        <v>251</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="121" ht="49.7" spans="1:7">
       <c r="A121" s="3">
-        <v>852</v>
+        <v>1262</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>285</v>
+        <v>251</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>287</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="122" ht="49.7" spans="1:7">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" ht="62.15" spans="1:7">
       <c r="A122" s="3">
-        <v>853</v>
+        <v>1263</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>287</v>
+        <v>251</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="123" ht="49.7" spans="1:7">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="123" ht="62.15" spans="1:7">
       <c r="A123" s="3">
-        <v>854</v>
+        <v>1264</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>289</v>
+        <v>251</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" ht="62.15" spans="1:7">
       <c r="A124" s="3">
-        <v>855</v>
+        <v>1265</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>291</v>
+        <v>251</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>293</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="125" ht="49.7" spans="1:7">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="125" ht="62.15" spans="1:7">
       <c r="A125" s="3">
-        <v>856</v>
+        <v>1266</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>293</v>
+        <v>251</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>295</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="126" ht="49.7" spans="1:7">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="126" ht="62.15" spans="1:7">
       <c r="A126" s="3">
-        <v>857</v>
+        <v>1267</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>295</v>
+        <v>251</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="127" ht="49.7" spans="1:7">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="127" ht="62.15" spans="1:7">
       <c r="A127" s="3">
-        <v>858</v>
+        <v>1268</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>297</v>
+        <v>251</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>299</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="128" ht="49.7" spans="1:7">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="128" ht="74.55" spans="1:7">
       <c r="A128" s="3">
-        <v>859</v>
+        <v>1269</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>299</v>
+        <v>251</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>301</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="129" ht="62.15" spans="1:7">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="129" ht="74.55" spans="1:7">
       <c r="A129" s="3">
-        <v>1054</v>
+        <v>1270</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>26</v>
+        <v>252</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>303</v>
@@ -5857,663 +5647,663 @@
     </row>
     <row r="130" ht="62.15" spans="1:7">
       <c r="A130" s="3">
-        <v>1069</v>
+        <v>1272</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D130" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E130" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F130" s="5" t="s">
+      <c r="G130" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="131" ht="62.15" spans="1:7">
       <c r="A131" s="3">
-        <v>1243</v>
+        <v>1273</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D131" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G131" s="6" t="s">
         <v>308</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="132" ht="62.15" spans="1:7">
       <c r="A132" s="3">
-        <v>1244</v>
+        <v>1274</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="E132" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F132" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>312</v>
-      </c>
       <c r="G132" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="133" ht="62.15" spans="1:7">
       <c r="A133" s="3">
-        <v>1245</v>
+        <v>1275</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="134" ht="62.15" spans="1:7">
       <c r="A134" s="3">
-        <v>1246</v>
+        <v>1276</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="F134" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="135" ht="62.15" spans="1:7">
+      <c r="A135" s="3">
+        <v>1277</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="G135" s="6" t="s">
         <v>316</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="135" ht="74.55" spans="1:7">
-      <c r="A135" s="3">
-        <v>1247</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="136" ht="62.15" spans="1:7">
       <c r="A136" s="3">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="F136" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="137" ht="74.55" spans="1:7">
+      <c r="A137" s="3">
+        <v>1279</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G137" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G136" s="6" t="s">
+    </row>
+    <row r="138" ht="74.55" spans="1:7">
+      <c r="A138" s="3">
+        <v>1280</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F138" s="5" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="137" ht="62.15" spans="1:7">
-      <c r="A137" s="3">
-        <v>1249</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F137" s="5" t="s">
+      <c r="G138" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G137" s="6" t="s">
+    </row>
+    <row r="139" ht="62.15" spans="1:7">
+      <c r="A139" s="3">
+        <v>1281</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F139" s="5" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="138" ht="49.7" spans="1:7">
-      <c r="A138" s="3">
-        <v>1250</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F138" s="5" t="s">
+      <c r="G139" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G138" s="6" t="s">
+    </row>
+    <row r="140" ht="62.15" spans="1:7">
+      <c r="A140" s="3">
+        <v>1282</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F140" s="5" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="139" ht="49.7" spans="1:7">
-      <c r="A139" s="3">
-        <v>1251</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F139" s="6" t="s">
+      <c r="G140" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="140" ht="49.7" spans="1:7">
-      <c r="A140" s="3">
-        <v>1252</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="141" ht="62.15" spans="1:7">
       <c r="A141" s="3">
-        <v>1253</v>
+        <v>1283</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" ht="62.15" spans="1:7">
       <c r="A142" s="3">
-        <v>1254</v>
+        <v>1284</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" ht="62.15" spans="1:7">
       <c r="A143" s="3">
-        <v>1255</v>
+        <v>1285</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F143" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="144" ht="74.55" spans="1:7">
+      <c r="A144" s="3">
+        <v>1286</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F144" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="G144" s="6" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="144" ht="62.15" spans="1:7">
-      <c r="A144" s="3">
-        <v>1256</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="145" ht="74.55" spans="1:7">
       <c r="A145" s="3">
-        <v>1257</v>
+        <v>1287</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="146" ht="62.15" spans="1:7">
       <c r="A146" s="3">
-        <v>1258</v>
+        <v>1288</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" ht="62.15" spans="1:7">
       <c r="A147" s="3">
-        <v>1259</v>
+        <v>1289</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F147" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="148" ht="62.15" spans="1:7">
+      <c r="A148" s="3">
+        <v>1293</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F148" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G148" s="6" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="148" ht="49.7" spans="1:7">
-      <c r="A148" s="3">
-        <v>1260</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F148" s="5" t="s">
+    <row r="149" ht="74.55" spans="1:7">
+      <c r="A149" s="3">
+        <v>1294</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G149" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="149" ht="49.7" spans="1:7">
-      <c r="A149" s="3">
-        <v>1261</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F149" s="6" t="s">
+    <row r="150" ht="62.15" spans="1:7">
+      <c r="A150" s="3">
+        <v>1297</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="E150" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F150" s="5" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="150" ht="49.7" spans="1:7">
-      <c r="A150" s="3">
-        <v>1262</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F150" s="5" t="s">
+      <c r="G150" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="151" ht="62.15" spans="1:7">
       <c r="A151" s="3">
-        <v>1263</v>
+        <v>1298</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F151" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G151" s="6" t="s">
         <v>350</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="152" ht="62.15" spans="1:7">
       <c r="A152" s="3">
-        <v>1264</v>
+        <v>1299</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F152" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G152" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="G152" s="6" t="s">
+    </row>
+    <row r="153" ht="74.55" spans="1:7">
+      <c r="A153" s="3">
+        <v>1300</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F153" s="5" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="153" ht="62.15" spans="1:7">
-      <c r="A153" s="3">
-        <v>1265</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F153" s="5" t="s">
+      <c r="G153" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G153" s="6" t="s">
+    </row>
+    <row r="154" ht="74.55" spans="1:7">
+      <c r="A154" s="3">
+        <v>1301</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="154" ht="62.15" spans="1:7">
-      <c r="A154" s="3">
-        <v>1266</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F154" s="5" t="s">
+      <c r="G154" s="6" t="s">
         <v>356</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="155" ht="62.15" spans="1:7">
       <c r="A155" s="3">
-        <v>1267</v>
+        <v>1302</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F155" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="G155" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="G155" s="6" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="156" ht="62.15" spans="1:7">
       <c r="A156" s="3">
-        <v>1268</v>
+        <v>1303</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F156" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G156" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="G156" s="6" t="s">
+    </row>
+    <row r="157" ht="62.15" spans="1:7">
+      <c r="A157" s="3">
+        <v>1307</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F157" s="5" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="157" ht="74.55" spans="1:7">
-      <c r="A157" s="3">
-        <v>1269</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F157" s="5" t="s">
+      <c r="G157" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G157" s="6" t="s">
+    </row>
+    <row r="158" ht="49.7" spans="1:7">
+      <c r="A158" s="3">
+        <v>1313</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D158" s="4" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="158" ht="74.55" spans="1:7">
-      <c r="A158" s="3">
-        <v>1270</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>308</v>
-      </c>
       <c r="E158" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>364</v>
@@ -6522,21 +6312,21 @@
         <v>365</v>
       </c>
     </row>
-    <row r="159" ht="62.15" spans="1:7">
+    <row r="159" ht="49.7" spans="1:7">
       <c r="A159" s="3">
-        <v>1271</v>
+        <v>1317</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>301</v>
+        <v>24</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>308</v>
+        <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>366</v>
@@ -6545,21 +6335,21 @@
         <v>367</v>
       </c>
     </row>
-    <row r="160" ht="62.15" spans="1:7">
+    <row r="160" ht="49.7" spans="1:7">
       <c r="A160" s="3">
-        <v>1272</v>
+        <v>1318</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>301</v>
+        <v>24</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>308</v>
+        <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>368</v>
@@ -6568,21 +6358,21 @@
         <v>369</v>
       </c>
     </row>
-    <row r="161" ht="62.15" spans="1:7">
+    <row r="161" ht="49.7" spans="1:7">
       <c r="A161" s="3">
-        <v>1273</v>
+        <v>1319</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>301</v>
+        <v>24</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>308</v>
+        <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>370</v>
@@ -6593,19 +6383,19 @@
     </row>
     <row r="162" ht="62.15" spans="1:7">
       <c r="A162" s="3">
-        <v>1274</v>
+        <v>1320</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>301</v>
+        <v>24</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>308</v>
+        <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>372</v>
@@ -6614,21 +6404,21 @@
         <v>373</v>
       </c>
     </row>
-    <row r="163" ht="62.15" spans="1:7">
+    <row r="163" ht="49.7" spans="1:7">
       <c r="A163" s="3">
-        <v>1275</v>
+        <v>1321</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>301</v>
+        <v>24</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>308</v>
+        <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>374</v>
@@ -6637,1774 +6427,1298 @@
         <v>375</v>
       </c>
     </row>
-    <row r="164" ht="62.15" spans="1:7">
+    <row r="164" ht="49.7" spans="1:7">
       <c r="A164" s="3">
-        <v>1276</v>
+        <v>2144</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>308</v>
+        <v>377</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F164" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="165" ht="74.55" spans="1:7">
+      <c r="A165" s="3">
+        <v>2250</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="G164" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="165" ht="62.15" spans="1:7">
-      <c r="A165" s="3">
-        <v>1277</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>301</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="166" ht="62.15" spans="1:7">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="166" ht="74.55" spans="1:7">
       <c r="A166" s="3">
-        <v>1278</v>
+        <v>2251</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="167" ht="74.55" spans="1:7">
       <c r="A167" s="3">
-        <v>1279</v>
+        <v>2252</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="168" ht="74.55" spans="1:7">
       <c r="A168" s="3">
-        <v>1280</v>
+        <v>2253</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="169" ht="62.15" spans="1:7">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="169" ht="87" spans="1:7">
       <c r="A169" s="3">
-        <v>1281</v>
+        <v>2254</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="170" ht="62.15" spans="1:7">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170" ht="87" spans="1:7">
       <c r="A170" s="3">
-        <v>1282</v>
+        <v>2255</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="171" ht="62.15" spans="1:7">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="171" ht="87" spans="1:7">
       <c r="A171" s="3">
-        <v>1283</v>
+        <v>2256</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="172" ht="62.15" spans="1:7">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="172" ht="87" spans="1:7">
       <c r="A172" s="3">
-        <v>1284</v>
+        <v>2257</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="173" ht="62.15" spans="1:7">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="173" ht="74.55" spans="1:7">
       <c r="A173" s="3">
-        <v>1285</v>
+        <v>2258</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="174" ht="74.55" spans="1:7">
       <c r="A174" s="3">
-        <v>1286</v>
+        <v>2259</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="175" ht="74.55" spans="1:7">
       <c r="A175" s="3">
-        <v>1287</v>
+        <v>2260</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="176" ht="62.15" spans="1:7">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="176" ht="74.55" spans="1:7">
       <c r="A176" s="3">
-        <v>1288</v>
+        <v>2261</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="177" ht="62.15" spans="1:7">
       <c r="A177" s="3">
-        <v>1289</v>
+        <v>2270</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="178" ht="62.15" spans="1:7">
       <c r="A178" s="3">
-        <v>1293</v>
+        <v>2271</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="179" ht="62.15" spans="1:7">
+      <c r="A179" s="3">
+        <v>2272</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D179" s="4" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="179" ht="74.55" spans="1:7">
-      <c r="A179" s="3">
-        <v>1294</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>390</v>
-      </c>
       <c r="E179" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="180" ht="62.15" spans="1:7">
       <c r="A180" s="3">
-        <v>1297</v>
+        <v>2273</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="181" ht="62.15" spans="1:7">
       <c r="A181" s="3">
-        <v>1298</v>
+        <v>2274</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="182" ht="62.15" spans="1:7">
       <c r="A182" s="3">
-        <v>1299</v>
+        <v>2275</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="183" ht="74.55" spans="1:7">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="183" ht="62.15" spans="1:7">
       <c r="A183" s="3">
-        <v>1300</v>
+        <v>2276</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="184" ht="74.55" spans="1:7">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="184" ht="62.15" spans="1:7">
       <c r="A184" s="3">
-        <v>1301</v>
+        <v>2277</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="185" ht="62.15" spans="1:7">
       <c r="A185" s="3">
-        <v>1302</v>
+        <v>2278</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" ht="62.15" spans="1:7">
       <c r="A186" s="3">
-        <v>1303</v>
+        <v>2279</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="187" ht="62.15" spans="1:7">
       <c r="A187" s="3">
-        <v>1307</v>
+        <v>2280</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G187" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="188" ht="62.15" spans="1:7">
+      <c r="A188" s="3">
+        <v>2281</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="189" ht="62.15" spans="1:7">
+      <c r="A189" s="3">
+        <v>2310</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D189" s="4" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="188" ht="49.7" spans="1:7">
-      <c r="A188" s="3">
-        <v>1313</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="E189" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F189" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="E188" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F188" s="5" t="s">
+      <c r="G189" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="G188" s="6" t="s">
+    </row>
+    <row r="190" ht="62.15" spans="1:7">
+      <c r="A190" s="3">
+        <v>2311</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F190" s="5" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="189" ht="49.7" spans="1:7">
-      <c r="A189" s="3">
-        <v>1317</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D189" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E189" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F189" s="5" t="s">
+      <c r="G190" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="G189" s="6" t="s">
+    </row>
+    <row r="191" ht="62.15" spans="1:7">
+      <c r="A191" s="3">
+        <v>2312</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F191" s="5" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="190" ht="49.7" spans="1:7">
-      <c r="A190" s="3">
-        <v>1318</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E190" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F190" s="5" t="s">
+      <c r="G191" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="G190" s="6" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="191" ht="49.7" spans="1:7">
-      <c r="A191" s="3">
-        <v>1319</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E191" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="G191" s="6" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="192" ht="62.15" spans="1:7">
       <c r="A192" s="3">
-        <v>1320</v>
+        <v>2575</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E192" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="E192" s="4"/>
       <c r="F192" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="193" ht="62.15" spans="1:7">
+      <c r="A193" s="3">
+        <v>2592</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D193" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="G192" s="6" t="s">
+      <c r="E193" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F193" s="5" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="193" ht="49.7" spans="1:7">
-      <c r="A193" s="3">
-        <v>1321</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E193" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F193" s="5" t="s">
+      <c r="G193" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G193" s="6" t="s">
+    </row>
+    <row r="194" ht="62.15" spans="1:7">
+      <c r="A194" s="3">
+        <v>2603</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D194" s="4" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="194" ht="49.7" spans="1:7">
-      <c r="A194" s="3">
-        <v>2144</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C194" s="4" t="s">
+      <c r="E194" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F194" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="G194" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E194" s="4" t="s">
+    </row>
+    <row r="195" ht="62.15" spans="1:7">
+      <c r="A195" s="3">
+        <v>2606</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F195" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="F194" s="6" t="s">
+      <c r="G195" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="G194" s="6" t="s">
+    </row>
+    <row r="196" ht="62.15" spans="1:7">
+      <c r="A196" s="3">
+        <v>2607</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F196" s="5" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="195" ht="49.7" spans="1:7">
-      <c r="A195" s="3">
-        <v>2145</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D195" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F195" s="6" t="s">
+      <c r="G196" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="G195" s="6" t="s">
+    </row>
+    <row r="197" ht="62.15" spans="1:7">
+      <c r="A197" s="3">
+        <v>2608</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F197" s="5" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="196" ht="49.7" spans="1:7">
-      <c r="A196" s="3">
-        <v>2146</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D196" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E196" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F196" s="6" t="s">
+      <c r="G197" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="G196" s="6" t="s">
+    </row>
+    <row r="198" ht="49.7" spans="1:7">
+      <c r="A198" s="3">
+        <v>2609</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F198" s="5" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="197" ht="49.7" spans="1:7">
-      <c r="A197" s="3">
-        <v>2147</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E197" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F197" s="6" t="s">
+      <c r="G198" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="G197" s="6" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="198" ht="62.15" spans="1:7">
-      <c r="A198" s="3">
-        <v>2148</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F198" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="G198" s="6" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="199" ht="74.55" spans="1:7">
+    </row>
+    <row r="199" ht="49.7" spans="1:7">
       <c r="A199" s="3">
-        <v>2250</v>
+        <v>2610</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G199" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="200" ht="74.55" spans="1:7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="200" ht="49.7" spans="1:7">
       <c r="A200" s="3">
-        <v>2251</v>
+        <v>2611</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="201" ht="74.55" spans="1:7">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="201" ht="49.7" spans="1:7">
       <c r="A201" s="3">
-        <v>2252</v>
+        <v>2612</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="202" ht="74.55" spans="1:7">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="202" ht="49.7" spans="1:7">
       <c r="A202" s="3">
-        <v>2253</v>
+        <v>2613</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="203" ht="87" spans="1:7">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="203" ht="62.15" spans="1:7">
       <c r="A203" s="3">
-        <v>2254</v>
+        <v>2614</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G203" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="204" ht="87" spans="1:7">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="204" ht="62.15" spans="1:7">
       <c r="A204" s="3">
-        <v>2255</v>
+        <v>2615</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="205" ht="87" spans="1:7">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="205" ht="62.15" spans="1:7">
       <c r="A205" s="3">
-        <v>2256</v>
+        <v>2616</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G205" s="6" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="206" ht="87" spans="1:7">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="206" ht="62.15" spans="1:7">
       <c r="A206" s="3">
-        <v>2257</v>
+        <v>2617</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>439</v>
+        <v>29</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="207" ht="74.55" spans="1:7">
-      <c r="A207" s="3">
-        <v>2258</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D207" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E207" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F207" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="G207" s="6" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="208" ht="74.55" spans="1:7">
-      <c r="A208" s="3">
-        <v>2259</v>
-      </c>
-      <c r="B208" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D208" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E208" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F208" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="G208" s="6" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="209" ht="74.55" spans="1:7">
-      <c r="A209" s="3">
-        <v>2260</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D209" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E209" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F209" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="G209" s="6" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="210" ht="74.55" spans="1:7">
-      <c r="A210" s="3">
-        <v>2261</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E210" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F210" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="G210" s="6" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="211" ht="62.15" spans="1:7">
-      <c r="A211" s="3">
-        <v>2270</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D211" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E211" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F211" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="G211" s="6" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="212" ht="62.15" spans="1:7">
-      <c r="A212" s="3">
-        <v>2271</v>
-      </c>
-      <c r="B212" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D212" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E212" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F212" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="G212" s="6" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="213" ht="62.15" spans="1:7">
-      <c r="A213" s="3">
-        <v>2272</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D213" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E213" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F213" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="G213" s="6" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="214" ht="62.15" spans="1:7">
-      <c r="A214" s="3">
-        <v>2273</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E214" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="G214" s="6" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="215" ht="62.15" spans="1:7">
-      <c r="A215" s="3">
-        <v>2274</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E215" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="G215" s="6" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="216" ht="62.15" spans="1:7">
-      <c r="A216" s="3">
-        <v>2275</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D216" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E216" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F216" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="G216" s="6" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="217" ht="62.15" spans="1:7">
-      <c r="A217" s="3">
-        <v>2276</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E217" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F217" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="G217" s="6" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="218" ht="62.15" spans="1:7">
-      <c r="A218" s="3">
-        <v>2277</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E218" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F218" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="G218" s="6" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="219" ht="62.15" spans="1:7">
-      <c r="A219" s="3">
-        <v>2278</v>
-      </c>
-      <c r="B219" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D219" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E219" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F219" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="G219" s="6" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="220" ht="62.15" spans="1:7">
-      <c r="A220" s="3">
-        <v>2279</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E220" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F220" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="G220" s="6" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="221" ht="62.15" spans="1:7">
-      <c r="A221" s="3">
-        <v>2280</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D221" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E221" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F221" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="G221" s="6" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="222" ht="62.15" spans="1:7">
-      <c r="A222" s="3">
-        <v>2281</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E222" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F222" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="G222" s="6" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="223" ht="62.15" spans="1:7">
-      <c r="A223" s="3">
-        <v>2310</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D223" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="E223" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="G223" s="6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="224" ht="62.15" spans="1:7">
-      <c r="A224" s="3">
-        <v>2311</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D224" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="E224" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="G224" s="6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="225" ht="62.15" spans="1:7">
-      <c r="A225" s="3">
-        <v>2312</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D225" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="E225" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="G225" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="226" ht="62.15" spans="1:7">
-      <c r="A226" s="3">
-        <v>2575</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="E226" s="4"/>
-      <c r="F226" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="G226" s="6" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="227" ht="62.15" spans="1:7">
-      <c r="A227" s="3">
-        <v>2592</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D227" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="E227" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="G227" s="6" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="228" ht="62.15" spans="1:7">
-      <c r="A228" s="3">
-        <v>2603</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="E228" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F228" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="G228" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="229" ht="62.15" spans="1:7">
-      <c r="A229" s="3">
-        <v>2606</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E229" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="G229" s="6" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="230" ht="62.15" spans="1:7">
-      <c r="A230" s="3">
-        <v>2607</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D230" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E230" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F230" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G230" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="231" ht="62.15" spans="1:7">
-      <c r="A231" s="3">
-        <v>2608</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D231" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E231" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="G231" s="6" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="232" ht="49.7" spans="1:7">
-      <c r="A232" s="3">
-        <v>2609</v>
-      </c>
-      <c r="B232" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D232" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E232" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="G232" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="233" ht="49.7" spans="1:7">
-      <c r="A233" s="3">
-        <v>2610</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D233" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E233" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="G233" s="6" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="234" ht="49.7" spans="1:7">
-      <c r="A234" s="3">
-        <v>2611</v>
-      </c>
-      <c r="B234" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D234" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E234" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F234" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="G234" s="6" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="235" ht="49.7" spans="1:7">
-      <c r="A235" s="3">
-        <v>2612</v>
-      </c>
-      <c r="B235" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D235" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E235" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G235" s="6" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="236" ht="49.7" spans="1:7">
-      <c r="A236" s="3">
-        <v>2613</v>
-      </c>
-      <c r="B236" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D236" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E236" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F236" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="G236" s="6" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="237" ht="62.15" spans="1:7">
-      <c r="A237" s="3">
-        <v>2614</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D237" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E237" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="G237" s="6" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="238" ht="62.15" spans="1:7">
-      <c r="A238" s="3">
-        <v>2615</v>
-      </c>
-      <c r="B238" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D238" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E238" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F238" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="G238" s="6" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="239" ht="62.15" spans="1:7">
-      <c r="A239" s="3">
-        <v>2616</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D239" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E239" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="G239" s="6" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="240" ht="62.15" spans="1:7">
-      <c r="A240" s="3">
-        <v>2617</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D240" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E240" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F240" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="G240" s="6" t="s">
-        <v>535</v>
-      </c>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="8"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="9"/>
+      <c r="D207" s="9"/>
+      <c r="E207" s="9"/>
+      <c r="F207" s="10"/>
+      <c r="G207" s="11"/>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="8"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="9"/>
+      <c r="D208" s="9"/>
+      <c r="E208" s="9"/>
+      <c r="F208" s="10"/>
+      <c r="G208" s="11"/>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="8"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
+      <c r="F209" s="10"/>
+      <c r="G209" s="11"/>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="8"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
+      <c r="F210" s="10"/>
+      <c r="G210" s="11"/>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="8"/>
+      <c r="B211" s="9"/>
+      <c r="C211" s="9"/>
+      <c r="D211" s="9"/>
+      <c r="E211" s="9"/>
+      <c r="F211" s="10"/>
+      <c r="G211" s="11"/>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="8"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="9"/>
+      <c r="E212" s="9"/>
+      <c r="F212" s="10"/>
+      <c r="G212" s="11"/>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="8"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
+      <c r="D213" s="9"/>
+      <c r="E213" s="9"/>
+      <c r="F213" s="10"/>
+      <c r="G213" s="11"/>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="8"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
+      <c r="D214" s="9"/>
+      <c r="E214" s="9"/>
+      <c r="F214" s="10"/>
+      <c r="G214" s="11"/>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="8"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
+      <c r="D215" s="9"/>
+      <c r="E215" s="9"/>
+      <c r="F215" s="10"/>
+      <c r="G215" s="11"/>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="8"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
+      <c r="F216" s="10"/>
+      <c r="G216" s="11"/>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="8"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="9"/>
+      <c r="D217" s="9"/>
+      <c r="E217" s="9"/>
+      <c r="F217" s="10"/>
+      <c r="G217" s="11"/>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="8"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
+      <c r="D218" s="9"/>
+      <c r="E218" s="9"/>
+      <c r="F218" s="10"/>
+      <c r="G218" s="11"/>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="8"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
+      <c r="D219" s="9"/>
+      <c r="E219" s="9"/>
+      <c r="F219" s="10"/>
+      <c r="G219" s="11"/>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="8"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
+      <c r="D220" s="9"/>
+      <c r="E220" s="9"/>
+      <c r="F220" s="10"/>
+      <c r="G220" s="11"/>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="8"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
+      <c r="F221" s="10"/>
+      <c r="G221" s="11"/>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="8"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
+      <c r="F222" s="10"/>
+      <c r="G222" s="11"/>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="8"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
+      <c r="D223" s="9"/>
+      <c r="E223" s="9"/>
+      <c r="F223" s="10"/>
+      <c r="G223" s="11"/>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="8"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
+      <c r="D224" s="9"/>
+      <c r="E224" s="9"/>
+      <c r="F224" s="10"/>
+      <c r="G224" s="11"/>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="8"/>
+      <c r="B225" s="9"/>
+      <c r="C225" s="9"/>
+      <c r="D225" s="9"/>
+      <c r="E225" s="9"/>
+      <c r="F225" s="10"/>
+      <c r="G225" s="11"/>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="8"/>
+      <c r="B226" s="9"/>
+      <c r="C226" s="9"/>
+      <c r="D226" s="9"/>
+      <c r="E226" s="9"/>
+      <c r="F226" s="10"/>
+      <c r="G226" s="11"/>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="8"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="9"/>
+      <c r="D227" s="9"/>
+      <c r="E227" s="9"/>
+      <c r="F227" s="10"/>
+      <c r="G227" s="11"/>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="8"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="9"/>
+      <c r="D228" s="9"/>
+      <c r="E228" s="9"/>
+      <c r="F228" s="10"/>
+      <c r="G228" s="11"/>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="8"/>
+      <c r="B229" s="9"/>
+      <c r="C229" s="9"/>
+      <c r="D229" s="9"/>
+      <c r="E229" s="9"/>
+      <c r="F229" s="10"/>
+      <c r="G229" s="11"/>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="8"/>
+      <c r="B230" s="9"/>
+      <c r="C230" s="9"/>
+      <c r="D230" s="9"/>
+      <c r="E230" s="9"/>
+      <c r="F230" s="10"/>
+      <c r="G230" s="11"/>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="8"/>
+      <c r="B231" s="9"/>
+      <c r="C231" s="9"/>
+      <c r="D231" s="9"/>
+      <c r="E231" s="9"/>
+      <c r="F231" s="10"/>
+      <c r="G231" s="11"/>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="8"/>
+      <c r="B232" s="9"/>
+      <c r="C232" s="9"/>
+      <c r="D232" s="9"/>
+      <c r="E232" s="9"/>
+      <c r="F232" s="10"/>
+      <c r="G232" s="11"/>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="8"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="9"/>
+      <c r="D233" s="9"/>
+      <c r="E233" s="9"/>
+      <c r="F233" s="10"/>
+      <c r="G233" s="11"/>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="8"/>
+      <c r="B234" s="9"/>
+      <c r="C234" s="9"/>
+      <c r="D234" s="9"/>
+      <c r="E234" s="9"/>
+      <c r="F234" s="10"/>
+      <c r="G234" s="11"/>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="8"/>
+      <c r="B235" s="9"/>
+      <c r="C235" s="9"/>
+      <c r="D235" s="9"/>
+      <c r="E235" s="9"/>
+      <c r="F235" s="10"/>
+      <c r="G235" s="11"/>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="8"/>
+      <c r="B236" s="9"/>
+      <c r="C236" s="9"/>
+      <c r="D236" s="9"/>
+      <c r="E236" s="9"/>
+      <c r="F236" s="10"/>
+      <c r="G236" s="11"/>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="8"/>
+      <c r="B237" s="9"/>
+      <c r="C237" s="9"/>
+      <c r="D237" s="9"/>
+      <c r="E237" s="9"/>
+      <c r="F237" s="10"/>
+      <c r="G237" s="11"/>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="8"/>
+      <c r="B238" s="9"/>
+      <c r="C238" s="9"/>
+      <c r="D238" s="9"/>
+      <c r="E238" s="9"/>
+      <c r="F238" s="10"/>
+      <c r="G238" s="11"/>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="8"/>
+      <c r="B239" s="9"/>
+      <c r="C239" s="9"/>
+      <c r="D239" s="9"/>
+      <c r="E239" s="9"/>
+      <c r="F239" s="10"/>
+      <c r="G239" s="11"/>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="8"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="9"/>
+      <c r="D240" s="9"/>
+      <c r="E240" s="9"/>
+      <c r="F240" s="10"/>
+      <c r="G240" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/创新支撑系统-功能点走查记录.xlsx
+++ b/创新支撑系统-功能点走查记录.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="535">
   <si>
     <t>序号</t>
   </si>
@@ -58,6 +58,66 @@
     <t>创新支撑系统</t>
   </si>
   <si>
+    <t>开放门户管理</t>
+  </si>
+  <si>
+    <t>接入步骤管理</t>
+  </si>
+  <si>
+    <t>\</t>
+  </si>
+  <si>
+    <t>对接入步骤管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>开放能力管理</t>
+  </si>
+  <si>
+    <t>接口示例管理</t>
+  </si>
+  <si>
+    <t>接口示例信息管理</t>
+  </si>
+  <si>
+    <t>对接口示例信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>接口错误码管理</t>
+  </si>
+  <si>
+    <t>接口错误码信息管理</t>
+  </si>
+  <si>
+    <t>对接口错误码信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>我的工单</t>
+  </si>
+  <si>
+    <t>工单填报</t>
+  </si>
+  <si>
+    <t>对工单填报进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单处理</t>
+  </si>
+  <si>
+    <t>对工单处理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单审批</t>
+  </si>
+  <si>
+    <t>对工单审批进行配置管理操作</t>
+  </si>
+  <si>
+    <t>全局搜索管理</t>
+  </si>
+  <si>
+    <t>对全局搜索管理进行配置管理操作</t>
+  </si>
+  <si>
     <t>权限管理</t>
   </si>
   <si>
@@ -112,9 +172,6 @@
     <t>手动通知管理</t>
   </si>
   <si>
-    <t>\</t>
-  </si>
-  <si>
     <t>手动通知信息管理</t>
   </si>
   <si>
@@ -160,9 +217,72 @@
     <t>门户首页配置</t>
   </si>
   <si>
+    <t>轮播图首页配置</t>
+  </si>
+  <si>
+    <t>轮播图查询</t>
+  </si>
+  <si>
+    <t>对轮播图查询进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告首页配置</t>
+  </si>
+  <si>
+    <t>通知公告首页配置新增</t>
+  </si>
+  <si>
+    <t>对通知公告首页配置新增进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告首页配置修改</t>
+  </si>
+  <si>
+    <t>对通知公告首页配置修改进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告首页配置删除</t>
+  </si>
+  <si>
+    <t>对通知公告首页配置删除进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告首页配置查看</t>
+  </si>
+  <si>
+    <t>对通知公告首页配置查看进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告首页配置查询</t>
+  </si>
+  <si>
+    <t>对通知公告首页配置查询进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告首页配置置顶</t>
+  </si>
+  <si>
+    <t>对通知公告首页配置置顶进行配置管理操作</t>
+  </si>
+  <si>
+    <t>接入步骤首页配置</t>
+  </si>
+  <si>
+    <t>接入步骤首页配置查询</t>
+  </si>
+  <si>
+    <t>对接入步骤首页配置查询进行配置管理操作</t>
+  </si>
+  <si>
     <t>应用案例首页配置</t>
   </si>
   <si>
+    <t>应用案例首页配置查看</t>
+  </si>
+  <si>
+    <t>对应用案例首页配置查看进行配置管理操作</t>
+  </si>
+  <si>
     <t>应用案例首页置顶</t>
   </si>
   <si>
@@ -172,6 +292,18 @@
     <t>开放能力首页配置</t>
   </si>
   <si>
+    <t>开放能力首页配置删除</t>
+  </si>
+  <si>
+    <t>对开放能力首页配置删除进行配置管理操作</t>
+  </si>
+  <si>
+    <t>开放能力首页配置查询</t>
+  </si>
+  <si>
+    <t>对开放能力首页配置查询进行配置管理操作</t>
+  </si>
+  <si>
     <t>开放能力首页置顶</t>
   </si>
   <si>
@@ -181,6 +313,18 @@
     <t>开发资源首页配置</t>
   </si>
   <si>
+    <t>开发资源首页配置查看</t>
+  </si>
+  <si>
+    <t>对开发资源首页配置查看进行配置管理操作</t>
+  </si>
+  <si>
+    <t>开发资源首页配置查询</t>
+  </si>
+  <si>
+    <t>对开发资源首页配置查询进行配置管理操作</t>
+  </si>
+  <si>
     <t>开发资源首页置顶</t>
   </si>
   <si>
@@ -190,6 +334,18 @@
     <t>开发指南首页配置</t>
   </si>
   <si>
+    <t>开发指南首页配置查看</t>
+  </si>
+  <si>
+    <t>对开发指南首页配置查看进行配置管理操作</t>
+  </si>
+  <si>
+    <t>开发指南首页配置查询</t>
+  </si>
+  <si>
+    <t>对开发指南首页配置查询进行配置管理操作</t>
+  </si>
+  <si>
     <t>开发指南首页置顶</t>
   </si>
   <si>
@@ -199,18 +355,24 @@
     <t>帮助中心首页配置</t>
   </si>
   <si>
+    <t>帮助首页配置查看</t>
+  </si>
+  <si>
+    <t>对帮助首页配置查看进行配置管理操作</t>
+  </si>
+  <si>
+    <t>帮助首页配置查询</t>
+  </si>
+  <si>
+    <t>对帮助首页配置查询进行配置管理操作</t>
+  </si>
+  <si>
     <t>帮助首页置顶</t>
   </si>
   <si>
     <t>对帮助首页置顶进行配置管理操作</t>
   </si>
   <si>
-    <t>开放门户管理</t>
-  </si>
-  <si>
-    <t>接入步骤管理</t>
-  </si>
-  <si>
     <t>接入步骤新增</t>
   </si>
   <si>
@@ -241,19 +403,22 @@
     <t>对接入步骤查询进行配置管理操作</t>
   </si>
   <si>
-    <t>开放能力管理</t>
-  </si>
-  <si>
-    <t>客户端API管理</t>
-  </si>
-  <si>
-    <t>客户端API文档目录移动</t>
-  </si>
-  <si>
-    <t>对客户端API文档目录移动进行配置管理操作</t>
-  </si>
-  <si>
-    <t>接口示例管理</t>
+    <t>接口示例新增</t>
+  </si>
+  <si>
+    <t>对接口示例新增进行配置管理操作</t>
+  </si>
+  <si>
+    <t>接口示例修改</t>
+  </si>
+  <si>
+    <t>对接口示例修改进行配置管理操作</t>
+  </si>
+  <si>
+    <t>接口示例删除</t>
+  </si>
+  <si>
+    <t>对接口示例删除进行配置管理操作</t>
   </si>
   <si>
     <t>接口示例批量删除</t>
@@ -268,13 +433,34 @@
     <t>对接口示例查询字段排序进行配置管理操作</t>
   </si>
   <si>
+    <t>接口示例查看</t>
+  </si>
+  <si>
+    <t>对接口示例查看进行配置管理操作</t>
+  </si>
+  <si>
     <t>接口示例查询</t>
   </si>
   <si>
     <t>对接口示例查询进行配置管理操作</t>
   </si>
   <si>
-    <t>接口错误码管理</t>
+    <t>接口错误码新增</t>
+  </si>
+  <si>
+    <t>对接口错误码新增进行配置管理操作</t>
+  </si>
+  <si>
+    <t>接口错误码修改</t>
+  </si>
+  <si>
+    <t>对接口错误码修改进行配置管理操作</t>
+  </si>
+  <si>
+    <t>接口错误码删除</t>
+  </si>
+  <si>
+    <t>对接口错误码删除进行配置管理操作</t>
   </si>
   <si>
     <t>接口错误码批量删除</t>
@@ -289,15 +475,18 @@
     <t>对接口错误码查询字段排序进行配置管理操作</t>
   </si>
   <si>
+    <t>接口错误码查看</t>
+  </si>
+  <si>
+    <t>对接口错误码查看进行配置管理操作</t>
+  </si>
+  <si>
     <t>接口错误码查询</t>
   </si>
   <si>
     <t>对接口错误码查询进行配置管理操作</t>
   </si>
   <si>
-    <t>我的工单</t>
-  </si>
-  <si>
     <t>我的工单新增</t>
   </si>
   <si>
@@ -379,19 +568,40 @@
     <t>对帮助版本记录进行配置管理操作</t>
   </si>
   <si>
-    <t>帮助文档目录移动</t>
-  </si>
-  <si>
-    <t>对帮助文档目录移动进行配置管理操作</t>
-  </si>
-  <si>
     <t>应用案例管理</t>
   </si>
   <si>
+    <t>应用案例查看</t>
+  </si>
+  <si>
+    <t>对应用案例查看进行配置管理操作</t>
+  </si>
+  <si>
     <t>应用案例版本记录</t>
   </si>
   <si>
     <t>对应用案例版本记录进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告管理</t>
+  </si>
+  <si>
+    <t>通知公告删除</t>
+  </si>
+  <si>
+    <t>对通知公告删除进行配置管理操作</t>
+  </si>
+  <si>
+    <t>通知公告查看</t>
+  </si>
+  <si>
+    <t>对通知公告查看进行配置管理操作</t>
+  </si>
+  <si>
+    <t>热搜词排序</t>
+  </si>
+  <si>
+    <t>对热搜词排序进行配置管理操作</t>
   </si>
   <si>
     <t>软件服务商工作台</t>
@@ -1439,7 +1649,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1457,6 +1667,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1611,12 +1827,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1983,16 +2205,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2001,37 +2220,37 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2046,74 +2265,77 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2129,26 +2351,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2701,9 +2914,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="62.15" spans="1:7">
+    <row r="2" ht="49.7" spans="1:7">
       <c r="A2" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
@@ -2718,15 +2931,15 @@
         <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="74.55" spans="1:7">
+    </row>
+    <row r="3" ht="62.15" spans="1:7">
       <c r="A3" s="3">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
@@ -2735,21 +2948,21 @@
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" ht="62.15" spans="1:7">
       <c r="A4" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
@@ -2758,1102 +2971,1102 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" ht="49.7" spans="1:7">
       <c r="A5" s="3">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="6" t="s">
+    </row>
+    <row r="6" ht="49.7" spans="1:7">
+      <c r="A6" s="3">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="62.15" spans="1:7">
-      <c r="A6" s="3">
-        <v>159</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="7" ht="49.7" spans="1:7">
+      <c r="A7" s="3">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="8" ht="49.7" spans="1:7">
+      <c r="A8" s="3">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="E8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="6" t="s">
+    </row>
+    <row r="9" ht="62.15" spans="1:7">
+      <c r="A9" s="3">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" ht="62.15" spans="1:7">
-      <c r="A7" s="3">
-        <v>428</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="6" t="s">
+    </row>
+    <row r="10" ht="74.55" spans="1:7">
+      <c r="A10" s="3">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" ht="62.15" spans="1:7">
-      <c r="A8" s="3">
-        <v>429</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="49.7" spans="1:7">
-      <c r="A9" s="3">
-        <v>430</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" ht="62.15" spans="1:7">
-      <c r="A10" s="3">
-        <v>431</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" ht="62.15" spans="1:7">
       <c r="A11" s="3">
-        <v>453</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="49.7" spans="1:7">
+      <c r="A12" s="3">
+        <v>65</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" ht="62.15" spans="1:7">
-      <c r="A12" s="3">
-        <v>459</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13" ht="62.15" spans="1:7">
       <c r="A13" s="3">
-        <v>465</v>
+        <v>159</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" ht="62.15" spans="1:7">
       <c r="A14" s="3">
-        <v>471</v>
+        <v>428</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="6" t="s">
+    </row>
+    <row r="15" ht="62.15" spans="1:7">
+      <c r="A15" s="3">
+        <v>429</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" ht="49.7" spans="1:7">
-      <c r="A15" s="3">
-        <v>477</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" ht="49.7" spans="1:7">
       <c r="A16" s="3">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="62.15" spans="1:7">
+      <c r="A17" s="3">
+        <v>431</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" ht="49.7" spans="1:7">
-      <c r="A17" s="3">
-        <v>484</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" ht="49.7" spans="1:7">
       <c r="A18" s="3">
-        <v>485</v>
+        <v>436</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="6" t="s">
+    </row>
+    <row r="19" ht="62.15" spans="1:7">
+      <c r="A19" s="3">
+        <v>438</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" ht="49.7" spans="1:7">
-      <c r="A19" s="3">
-        <v>486</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" ht="49.7" spans="1:7">
+    <row r="20" ht="62.15" spans="1:7">
       <c r="A20" s="3">
-        <v>487</v>
+        <v>439</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="21" ht="62.15" spans="1:7">
       <c r="A21" s="3">
-        <v>531</v>
+        <v>440</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" ht="62.15" spans="1:7">
       <c r="A22" s="3">
-        <v>535</v>
+        <v>441</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="62.15" spans="1:7">
       <c r="A23" s="3">
-        <v>536</v>
+        <v>442</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" ht="62.15" spans="1:7">
+      <c r="A24" s="3">
+        <v>443</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" ht="49.7" spans="1:7">
-      <c r="A24" s="3">
-        <v>538</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="25" ht="62.15" spans="1:7">
       <c r="A25" s="3">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="26" ht="62.15" spans="1:7">
       <c r="A26" s="3">
-        <v>543</v>
+        <v>451</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" ht="49.7" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" ht="62.15" spans="1:7">
       <c r="A27" s="3">
-        <v>545</v>
+        <v>453</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" ht="62.15" spans="1:7">
+      <c r="A28" s="3">
+        <v>456</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" ht="49.7" spans="1:7">
-      <c r="A28" s="3">
-        <v>546</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="G28" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="5" t="s">
+    </row>
+    <row r="29" ht="62.15" spans="1:7">
+      <c r="A29" s="3">
+        <v>458</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" ht="49.7" spans="1:7">
-      <c r="A29" s="3">
-        <v>547</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="5" t="s">
+    <row r="30" ht="62.15" spans="1:7">
+      <c r="A30" s="3">
+        <v>459</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="30" ht="49.7" spans="1:7">
-      <c r="A30" s="3">
-        <v>548</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="31" ht="62.15" spans="1:7">
       <c r="A31" s="3">
-        <v>549</v>
+        <v>463</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="6" t="s">
+    </row>
+    <row r="32" ht="62.15" spans="1:7">
+      <c r="A32" s="3">
+        <v>464</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="32" ht="49.7" spans="1:7">
-      <c r="A32" s="3">
-        <v>550</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G32" s="6" t="s">
+    </row>
+    <row r="33" ht="62.15" spans="1:7">
+      <c r="A33" s="3">
+        <v>465</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="33" ht="49.7" spans="1:7">
-      <c r="A33" s="3">
-        <v>551</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="6" t="s">
+    </row>
+    <row r="34" ht="62.15" spans="1:7">
+      <c r="A34" s="3">
+        <v>469</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="34" ht="49.7" spans="1:7">
-      <c r="A34" s="3">
-        <v>552</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" ht="49.7" spans="1:7">
+    <row r="35" ht="62.15" spans="1:7">
       <c r="A35" s="3">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="36" ht="49.7" spans="1:7">
+    <row r="36" ht="62.15" spans="1:7">
       <c r="A36" s="3">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F36" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="37" ht="49.7" spans="1:7">
+    <row r="37" ht="62.15" spans="1:7">
       <c r="A37" s="3">
-        <v>555</v>
+        <v>475</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="F37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" ht="62.15" spans="1:7">
+      <c r="A38" s="3">
+        <v>476</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" ht="49.7" spans="1:7">
-      <c r="A38" s="3">
-        <v>556</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="F38" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" s="6" t="s">
         <v>109</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="39" ht="49.7" spans="1:7">
       <c r="A39" s="3">
-        <v>557</v>
+        <v>477</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>111</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="40" ht="49.7" spans="1:7">
       <c r="A40" s="3">
-        <v>564</v>
+        <v>483</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="41" ht="62.15" spans="1:7">
+    <row r="41" ht="49.7" spans="1:7">
       <c r="A41" s="3">
-        <v>568</v>
+        <v>484</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" ht="62.15" spans="1:7">
+    <row r="42" ht="49.7" spans="1:7">
       <c r="A42" s="3">
-        <v>575</v>
+        <v>485</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G42" s="6" t="s">
+    </row>
+    <row r="43" ht="49.7" spans="1:7">
+      <c r="A43" s="3">
+        <v>486</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="43" ht="62.15" spans="1:7">
-      <c r="A43" s="3">
-        <v>601</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="G43" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="4" t="s">
+    </row>
+    <row r="44" ht="49.7" spans="1:7">
+      <c r="A44" s="3">
+        <v>487</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G43" s="6" t="s">
+    </row>
+    <row r="45" ht="49.7" spans="1:7">
+      <c r="A45" s="3">
+        <v>532</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="44" ht="74.55" spans="1:7">
-      <c r="A44" s="3">
-        <v>621</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="G45" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="5" t="s">
+    </row>
+    <row r="46" ht="49.7" spans="1:7">
+      <c r="A46" s="3">
+        <v>533</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G46" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="45" ht="74.55" spans="1:7">
-      <c r="A45" s="3">
-        <v>622</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F45" s="5" t="s">
+    <row r="47" ht="49.7" spans="1:7">
+      <c r="A47" s="3">
+        <v>534</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G47" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="46" ht="74.55" spans="1:7">
-      <c r="A46" s="3">
-        <v>623</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F46" s="5" t="s">
+    <row r="48" ht="62.15" spans="1:7">
+      <c r="A48" s="3">
+        <v>535</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G48" s="5" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="47" ht="74.55" spans="1:7">
-      <c r="A47" s="3">
-        <v>624</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" ht="87" spans="1:7">
-      <c r="A48" s="3">
-        <v>633</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="49" ht="62.15" spans="1:7">
       <c r="A49" s="3">
-        <v>638</v>
+        <v>536</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>136</v>
+        <v>13</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="50" ht="49.7" spans="1:7">
       <c r="A50" s="3">
-        <v>639</v>
+        <v>537</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>139</v>
+        <v>13</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="51" ht="49.7" spans="1:7">
       <c r="A51" s="3">
-        <v>640</v>
+        <v>538</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>141</v>
+        <v>13</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="52" ht="49.7" spans="1:7">
       <c r="A52" s="3">
-        <v>678</v>
+        <v>539</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>7</v>
@@ -3862,21 +4075,21 @@
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>143</v>
+        <v>16</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="53" ht="49.7" spans="1:7">
       <c r="A53" s="3">
-        <v>679</v>
+        <v>540</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>7</v>
@@ -3885,21 +4098,21 @@
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>145</v>
+        <v>16</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="54" ht="49.7" spans="1:7">
       <c r="A54" s="3">
-        <v>680</v>
+        <v>541</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>7</v>
@@ -3908,21 +4121,21 @@
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>147</v>
+        <v>16</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="55" ht="62.15" spans="1:7">
       <c r="A55" s="3">
-        <v>681</v>
+        <v>542</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>7</v>
@@ -3931,21 +4144,21 @@
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>149</v>
+        <v>16</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="56" ht="62.15" spans="1:7">
       <c r="A56" s="3">
-        <v>682</v>
+        <v>543</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>7</v>
@@ -3954,21 +4167,21 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>151</v>
+        <v>16</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="57" ht="49.7" spans="1:7">
       <c r="A57" s="3">
-        <v>683</v>
+        <v>544</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>7</v>
@@ -3977,21 +4190,21 @@
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>153</v>
+        <v>16</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="58" ht="49.7" spans="1:7">
       <c r="A58" s="3">
-        <v>684</v>
+        <v>545</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>7</v>
@@ -4000,21 +4213,21 @@
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" ht="62.15" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" ht="49.7" spans="1:7">
       <c r="A59" s="3">
-        <v>685</v>
+        <v>546</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>7</v>
@@ -4023,21 +4236,21 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" ht="49.7" spans="1:7">
       <c r="A60" s="3">
-        <v>686</v>
+        <v>547</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>7</v>
@@ -4046,21 +4259,21 @@
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="61" ht="49.7" spans="1:7">
       <c r="A61" s="3">
-        <v>687</v>
+        <v>548</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>7</v>
@@ -4069,21 +4282,21 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>161</v>
+        <v>10</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="62" ht="62.15" spans="1:7">
       <c r="A62" s="3">
-        <v>688</v>
+        <v>549</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>7</v>
@@ -4092,21 +4305,21 @@
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="63" ht="74.55" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" ht="49.7" spans="1:7">
       <c r="A63" s="3">
-        <v>689</v>
+        <v>550</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>7</v>
@@ -4115,21 +4328,21 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="64" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" ht="49.7" spans="1:7">
       <c r="A64" s="3">
-        <v>690</v>
+        <v>551</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>7</v>
@@ -4138,21 +4351,21 @@
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="65" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="65" ht="49.7" spans="1:7">
       <c r="A65" s="3">
-        <v>691</v>
+        <v>552</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>7</v>
@@ -4161,21 +4374,21 @@
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>169</v>
+        <v>10</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="66" ht="49.7" spans="1:7">
       <c r="A66" s="3">
-        <v>692</v>
+        <v>553</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>7</v>
@@ -4184,21 +4397,21 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>171</v>
+        <v>10</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="67" ht="49.7" spans="1:7">
       <c r="A67" s="3">
-        <v>693</v>
+        <v>554</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>7</v>
@@ -4207,21 +4420,21 @@
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>173</v>
+        <v>10</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="68" ht="49.7" spans="1:7">
       <c r="A68" s="3">
-        <v>694</v>
+        <v>555</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>7</v>
@@ -4230,21 +4443,21 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="69" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" ht="49.7" spans="1:7">
       <c r="A69" s="3">
-        <v>695</v>
+        <v>556</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>7</v>
@@ -4253,21 +4466,21 @@
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="70" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" ht="49.7" spans="1:7">
       <c r="A70" s="3">
-        <v>696</v>
+        <v>557</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>7</v>
@@ -4276,21 +4489,21 @@
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>179</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="71" ht="49.7" spans="1:7">
       <c r="A71" s="3">
-        <v>697</v>
+        <v>564</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>7</v>
@@ -4299,21 +4512,21 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>181</v>
+        <v>176</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="72" ht="49.7" spans="1:7">
       <c r="A72" s="3">
-        <v>698</v>
+        <v>572</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>7</v>
@@ -4322,21 +4535,21 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="73" ht="62.15" spans="1:7">
       <c r="A73" s="3">
-        <v>707</v>
+        <v>575</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>7</v>
@@ -4345,21 +4558,21 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="74" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="74" ht="49.7" spans="1:7">
       <c r="A74" s="3">
-        <v>708</v>
+        <v>578</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>7</v>
@@ -4368,21 +4581,21 @@
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="E74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F74" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="75" ht="62.15" spans="1:7">
+      <c r="G74" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="75" ht="49.7" spans="1:7">
       <c r="A75" s="3">
-        <v>709</v>
+        <v>582</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>7</v>
@@ -4391,21 +4604,21 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>184</v>
+        <v>10</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="76" ht="62.15" spans="1:7">
+        <v>186</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="76" ht="49.7" spans="1:7">
       <c r="A76" s="3">
-        <v>710</v>
+        <v>597</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>7</v>
@@ -4414,3311 +4627,3787 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F76" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="77" ht="62.15" spans="1:7">
+      <c r="A77" s="3">
+        <v>601</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="E77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" s="7" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="77" ht="74.55" spans="1:7">
-      <c r="A77" s="3">
-        <v>711</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G77" s="6" t="s">
+    </row>
+    <row r="78" ht="74.55" spans="1:7">
+      <c r="A78" s="3">
+        <v>621</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="78" ht="62.15" spans="1:7">
-      <c r="A78" s="3">
-        <v>712</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E78" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F78" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="79" ht="62.15" spans="1:7">
+    <row r="79" ht="74.55" spans="1:7">
       <c r="A79" s="3">
-        <v>713</v>
+        <v>622</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F79" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G79" s="5" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="80" ht="49.7" spans="1:7">
+    <row r="80" ht="74.55" spans="1:7">
       <c r="A80" s="3">
-        <v>714</v>
+        <v>623</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F80" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="81" ht="49.7" spans="1:7">
+    <row r="81" ht="74.55" spans="1:7">
       <c r="A81" s="3">
-        <v>749</v>
+        <v>624</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="G81" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F81" s="5" t="s">
+    </row>
+    <row r="82" ht="87" spans="1:7">
+      <c r="A82" s="3">
+        <v>633</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G82" s="5" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="82" ht="49.7" spans="1:7">
-      <c r="A82" s="3">
-        <v>761</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E82" s="4" t="s">
+    <row r="83" ht="62.15" spans="1:7">
+      <c r="A83" s="3">
+        <v>638</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="G83" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G82" s="6" t="s">
+    </row>
+    <row r="84" ht="49.7" spans="1:7">
+      <c r="A84" s="3">
+        <v>639</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="83" ht="49.7" spans="1:7">
-      <c r="A83" s="3">
-        <v>768</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="84" ht="62.15" spans="1:7">
-      <c r="A84" s="3">
-        <v>787</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="E84" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F84" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G84" s="6" t="s">
+      <c r="G84" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="85" ht="62.15" spans="1:7">
+    <row r="85" ht="49.7" spans="1:7">
       <c r="A85" s="3">
-        <v>788</v>
+        <v>640</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F85" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="G85" s="6" t="s">
+      <c r="G85" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="86" ht="74.55" spans="1:7">
+    <row r="86" ht="49.7" spans="1:7">
       <c r="A86" s="3">
-        <v>789</v>
+        <v>678</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F86" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F86" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="G86" s="6" t="s">
+      <c r="G86" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="87" ht="62.15" spans="1:7">
+    <row r="87" ht="49.7" spans="1:7">
       <c r="A87" s="3">
-        <v>797</v>
+        <v>679</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F87" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="G87" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="88" ht="74.55" spans="1:7">
+    <row r="88" ht="49.7" spans="1:7">
       <c r="A88" s="3">
-        <v>798</v>
+        <v>680</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F88" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G88" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="89" ht="62.15" spans="1:7">
       <c r="A89" s="3">
-        <v>804</v>
+        <v>681</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F89" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F89" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="G89" s="6" t="s">
+      <c r="G89" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="90" ht="74.55" spans="1:7">
+    <row r="90" ht="62.15" spans="1:7">
       <c r="A90" s="3">
-        <v>805</v>
+        <v>682</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F90" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F90" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="G90" s="6" t="s">
+      <c r="G90" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="91" ht="62.15" spans="1:7">
+    <row r="91" ht="49.7" spans="1:7">
       <c r="A91" s="3">
-        <v>811</v>
+        <v>683</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F91" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F91" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="G91" s="6" t="s">
+      <c r="G91" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="92" ht="74.55" spans="1:7">
+    <row r="92" ht="49.7" spans="1:7">
       <c r="A92" s="3">
-        <v>812</v>
+        <v>684</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F92" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F92" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="G92" s="6" t="s">
+      <c r="G92" s="5" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="93" ht="49.7" spans="1:7">
+    <row r="93" ht="62.15" spans="1:7">
       <c r="A93" s="3">
-        <v>851</v>
+        <v>685</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F93" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F93" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="G93" s="6" t="s">
+      <c r="G93" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="94" ht="49.7" spans="1:7">
+    <row r="94" ht="62.15" spans="1:7">
       <c r="A94" s="3">
-        <v>852</v>
+        <v>686</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F94" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="G94" s="6" t="s">
+      <c r="G94" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="95" ht="49.7" spans="1:7">
+    <row r="95" ht="62.15" spans="1:7">
       <c r="A95" s="3">
-        <v>853</v>
+        <v>687</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F95" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="G95" s="6" t="s">
+      <c r="G95" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="96" ht="49.7" spans="1:7">
+    <row r="96" ht="62.15" spans="1:7">
       <c r="A96" s="3">
-        <v>854</v>
+        <v>688</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F96" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="G96" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="97" ht="62.15" spans="1:7">
+    <row r="97" ht="74.55" spans="1:7">
       <c r="A97" s="3">
-        <v>855</v>
+        <v>689</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F97" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="G97" s="6" t="s">
+      <c r="G97" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="98" ht="49.7" spans="1:7">
+    <row r="98" ht="62.15" spans="1:7">
       <c r="A98" s="3">
-        <v>856</v>
+        <v>690</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F98" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F98" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G98" s="6" t="s">
+      <c r="G98" s="5" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="99" ht="49.7" spans="1:7">
+    <row r="99" ht="62.15" spans="1:7">
       <c r="A99" s="3">
-        <v>857</v>
+        <v>691</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F99" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="G99" s="6" t="s">
+      <c r="G99" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="100" ht="49.7" spans="1:7">
       <c r="A100" s="3">
-        <v>858</v>
+        <v>692</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="G100" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="101" ht="49.7" spans="1:7">
       <c r="A101" s="3">
-        <v>859</v>
+        <v>693</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F101" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F101" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G101" s="5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="102" ht="62.15" spans="1:7">
+    <row r="102" ht="49.7" spans="1:7">
       <c r="A102" s="3">
-        <v>1054</v>
+        <v>694</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="G102" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="103" ht="62.15" spans="1:7">
       <c r="A103" s="3">
-        <v>1069</v>
+        <v>695</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>248</v>
+        <v>29</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>250</v>
+        <v>36</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="104" ht="62.15" spans="1:7">
       <c r="A104" s="3">
-        <v>1243</v>
+        <v>696</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="D104" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="105" ht="49.7" spans="1:7">
+      <c r="A105" s="3">
+        <v>697</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G105" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E104" s="4" t="s">
+    </row>
+    <row r="106" ht="49.7" spans="1:7">
+      <c r="A106" s="3">
+        <v>698</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="G106" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="105" ht="62.15" spans="1:7">
-      <c r="A105" s="3">
-        <v>1244</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="106" ht="62.15" spans="1:7">
-      <c r="A106" s="3">
-        <v>1245</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="107" ht="62.15" spans="1:7">
       <c r="A107" s="3">
-        <v>1246</v>
+        <v>707</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="108" ht="74.55" spans="1:7">
+        <v>254</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" ht="62.15" spans="1:7">
       <c r="A108" s="3">
-        <v>1247</v>
+        <v>708</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>262</v>
+        <v>254</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="109" ht="62.15" spans="1:7">
       <c r="A109" s="3">
-        <v>1249</v>
+        <v>709</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F109" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110" ht="62.15" spans="1:7">
+      <c r="A110" s="3">
+        <v>710</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="111" ht="74.55" spans="1:7">
+      <c r="A111" s="3">
+        <v>711</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F111" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="G109" s="6" t="s">
+      <c r="G111" s="5" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="110" ht="49.7" spans="1:7">
-      <c r="A110" s="3">
-        <v>1250</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F110" s="5" t="s">
+    <row r="112" ht="62.15" spans="1:7">
+      <c r="A112" s="3">
+        <v>712</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F112" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="G110" s="6" t="s">
+      <c r="G112" s="5" t="s">
         <v>266</v>
-      </c>
-    </row>
-    <row r="111" ht="49.7" spans="1:7">
-      <c r="A111" s="3">
-        <v>1251</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="112" ht="49.7" spans="1:7">
-      <c r="A112" s="3">
-        <v>1252</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="113" ht="62.15" spans="1:7">
       <c r="A113" s="3">
-        <v>1253</v>
+        <v>713</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F113" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="114" ht="49.7" spans="1:7">
+      <c r="A114" s="3">
+        <v>714</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="115" ht="49.7" spans="1:7">
+      <c r="A115" s="3">
+        <v>749</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G113" s="6" t="s">
+      <c r="E115" s="4" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="114" ht="62.15" spans="1:7">
-      <c r="A114" s="3">
-        <v>1254</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F114" s="5" t="s">
+      <c r="F115" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="G114" s="6" t="s">
+      <c r="G115" s="5" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="115" ht="62.15" spans="1:7">
-      <c r="A115" s="3">
-        <v>1255</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F115" s="5" t="s">
+    <row r="116" ht="49.7" spans="1:7">
+      <c r="A116" s="3">
+        <v>761</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="G115" s="6" t="s">
+      <c r="F116" s="7" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="116" ht="62.15" spans="1:7">
-      <c r="A116" s="3">
-        <v>1256</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F116" s="5" t="s">
+      <c r="G116" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G116" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="117" ht="74.55" spans="1:7">
+    </row>
+    <row r="117" ht="49.7" spans="1:7">
       <c r="A117" s="3">
-        <v>1257</v>
+        <v>768</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="118" ht="62.15" spans="1:7">
       <c r="A118" s="3">
-        <v>1259</v>
+        <v>787</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="F118" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="119" ht="62.15" spans="1:7">
+      <c r="A119" s="3">
+        <v>788</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G118" s="6" t="s">
+    </row>
+    <row r="120" ht="74.55" spans="1:7">
+      <c r="A120" s="3">
+        <v>789</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F120" s="7" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="119" ht="49.7" spans="1:7">
-      <c r="A119" s="3">
-        <v>1260</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F119" s="5" t="s">
+      <c r="G120" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G119" s="6" t="s">
+    </row>
+    <row r="121" ht="62.15" spans="1:7">
+      <c r="A121" s="3">
+        <v>797</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F121" s="5" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="120" ht="49.7" spans="1:7">
-      <c r="A120" s="3">
-        <v>1261</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F120" s="6" t="s">
+      <c r="G121" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G120" s="6" t="s">
+    </row>
+    <row r="122" ht="74.55" spans="1:7">
+      <c r="A122" s="3">
+        <v>798</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F122" s="7" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="121" ht="49.7" spans="1:7">
-      <c r="A121" s="3">
-        <v>1262</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F121" s="5" t="s">
+      <c r="G122" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="122" ht="62.15" spans="1:7">
-      <c r="A122" s="3">
-        <v>1263</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="123" ht="62.15" spans="1:7">
       <c r="A123" s="3">
-        <v>1264</v>
+        <v>804</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F123" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="124" ht="74.55" spans="1:7">
+      <c r="A124" s="3">
+        <v>805</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G124" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="124" ht="62.15" spans="1:7">
-      <c r="A124" s="3">
-        <v>1265</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" ht="62.15" spans="1:7">
       <c r="A125" s="3">
-        <v>1266</v>
+        <v>811</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F125" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="126" ht="74.55" spans="1:7">
+      <c r="A126" s="3">
+        <v>812</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G126" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="G125" s="6" t="s">
+    </row>
+    <row r="127" ht="49.7" spans="1:7">
+      <c r="A127" s="3">
+        <v>851</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" s="5" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="126" ht="62.15" spans="1:7">
-      <c r="A126" s="3">
-        <v>1267</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F126" s="5" t="s">
+      <c r="G127" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="G126" s="6" t="s">
+    </row>
+    <row r="128" ht="49.7" spans="1:7">
+      <c r="A128" s="3">
+        <v>852</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" s="5" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="127" ht="62.15" spans="1:7">
-      <c r="A127" s="3">
-        <v>1268</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F127" s="5" t="s">
+      <c r="G128" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G127" s="6" t="s">
+    </row>
+    <row r="129" ht="49.7" spans="1:7">
+      <c r="A129" s="3">
+        <v>853</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="128" ht="74.55" spans="1:7">
-      <c r="A128" s="3">
-        <v>1269</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F128" s="5" t="s">
+      <c r="G129" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="G128" s="6" t="s">
+    </row>
+    <row r="130" ht="49.7" spans="1:7">
+      <c r="A130" s="3">
+        <v>854</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="129" ht="74.55" spans="1:7">
-      <c r="A129" s="3">
-        <v>1270</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F129" s="5" t="s">
+      <c r="G130" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="G129" s="6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="130" ht="62.15" spans="1:7">
-      <c r="A130" s="3">
-        <v>1272</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="131" ht="62.15" spans="1:7">
       <c r="A131" s="3">
-        <v>1273</v>
+        <v>855</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>252</v>
+        <v>40</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="F131" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="132" ht="49.7" spans="1:7">
+      <c r="A132" s="3">
+        <v>856</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G132" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="G131" s="6" t="s">
+    </row>
+    <row r="133" ht="49.7" spans="1:7">
+      <c r="A133" s="3">
+        <v>857</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F133" s="5" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="132" ht="62.15" spans="1:7">
-      <c r="A132" s="3">
-        <v>1274</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F132" s="5" t="s">
+      <c r="G133" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="G132" s="6" t="s">
+    </row>
+    <row r="134" ht="49.7" spans="1:7">
+      <c r="A134" s="3">
+        <v>858</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="133" ht="62.15" spans="1:7">
-      <c r="A133" s="3">
-        <v>1275</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F133" s="5" t="s">
+      <c r="G134" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="G133" s="6" t="s">
+    </row>
+    <row r="135" ht="49.7" spans="1:7">
+      <c r="A135" s="3">
+        <v>859</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" s="5" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="134" ht="62.15" spans="1:7">
-      <c r="A134" s="3">
-        <v>1276</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F134" s="5" t="s">
+      <c r="G135" s="5" t="s">
         <v>313</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="135" ht="62.15" spans="1:7">
-      <c r="A135" s="3">
-        <v>1277</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="136" ht="62.15" spans="1:7">
       <c r="A136" s="3">
-        <v>1278</v>
+        <v>1054</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F136" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G136" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="G136" s="6" t="s">
+    </row>
+    <row r="137" ht="62.15" spans="1:7">
+      <c r="A137" s="3">
+        <v>1069</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="137" ht="74.55" spans="1:7">
-      <c r="A137" s="3">
-        <v>1279</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="E137" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F137" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="G137" s="6" t="s">
+      <c r="G137" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="138" ht="74.55" spans="1:7">
+    <row r="138" ht="62.15" spans="1:7">
       <c r="A138" s="3">
-        <v>1280</v>
+        <v>1243</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G138" s="6" t="s">
         <v>322</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="139" ht="62.15" spans="1:7">
       <c r="A139" s="3">
-        <v>1281</v>
+        <v>1244</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="140" ht="62.15" spans="1:7">
       <c r="A140" s="3">
-        <v>1282</v>
+        <v>1245</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="141" ht="62.15" spans="1:7">
       <c r="A141" s="3">
-        <v>1283</v>
+        <v>1246</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G141" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F141" s="7" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="142" ht="62.15" spans="1:7">
+      <c r="G141" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="142" ht="74.55" spans="1:7">
       <c r="A142" s="3">
-        <v>1284</v>
+        <v>1247</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G142" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F142" s="7" t="s">
         <v>331</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="143" ht="62.15" spans="1:7">
       <c r="A143" s="3">
-        <v>1285</v>
+        <v>1249</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="G143" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F143" s="7" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="144" ht="74.55" spans="1:7">
+      <c r="G143" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="144" ht="49.7" spans="1:7">
       <c r="A144" s="3">
-        <v>1286</v>
+        <v>1250</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="G144" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="145" ht="74.55" spans="1:7">
+      <c r="G144" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="145" ht="49.7" spans="1:7">
       <c r="A145" s="3">
-        <v>1287</v>
+        <v>1251</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="G145" s="6" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="146" ht="62.15" spans="1:7">
+      <c r="G145" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="146" ht="49.7" spans="1:7">
       <c r="A146" s="3">
-        <v>1288</v>
+        <v>1252</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G146" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F146" s="7" t="s">
         <v>339</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="147" ht="62.15" spans="1:7">
       <c r="A147" s="3">
-        <v>1289</v>
+        <v>1253</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="G147" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F147" s="7" t="s">
         <v>341</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="148" ht="62.15" spans="1:7">
       <c r="A148" s="3">
-        <v>1293</v>
+        <v>1254</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="G148" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F148" s="7" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="149" ht="74.55" spans="1:7">
+      <c r="G148" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="149" ht="62.15" spans="1:7">
       <c r="A149" s="3">
-        <v>1294</v>
+        <v>1255</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="G149" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F149" s="7" t="s">
         <v>345</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="150" ht="62.15" spans="1:7">
       <c r="A150" s="3">
-        <v>1297</v>
+        <v>1256</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F150" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F150" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="G150" s="6" t="s">
+      <c r="G150" s="5" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="151" ht="62.15" spans="1:7">
+    <row r="151" ht="74.55" spans="1:7">
       <c r="A151" s="3">
-        <v>1298</v>
+        <v>1257</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F151" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F151" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="G151" s="6" t="s">
+      <c r="G151" s="5" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="152" ht="62.15" spans="1:7">
       <c r="A152" s="3">
-        <v>1299</v>
+        <v>1259</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F152" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F152" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="G152" s="6" t="s">
+      <c r="G152" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="153" ht="74.55" spans="1:7">
+    <row r="153" ht="49.7" spans="1:7">
       <c r="A153" s="3">
-        <v>1300</v>
+        <v>1260</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F153" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F153" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G153" s="6" t="s">
+      <c r="G153" s="5" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="154" ht="74.55" spans="1:7">
+    <row r="154" ht="49.7" spans="1:7">
       <c r="A154" s="3">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G154" s="5" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="155" ht="62.15" spans="1:7">
+    <row r="155" ht="49.7" spans="1:7">
       <c r="A155" s="3">
-        <v>1302</v>
+        <v>1262</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F155" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F155" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="G155" s="6" t="s">
+      <c r="G155" s="5" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="156" ht="62.15" spans="1:7">
       <c r="A156" s="3">
-        <v>1303</v>
+        <v>1263</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F156" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F156" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="G156" s="6" t="s">
+      <c r="G156" s="5" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="157" ht="62.15" spans="1:7">
       <c r="A157" s="3">
-        <v>1307</v>
+        <v>1264</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F157" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F157" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="G157" s="6" t="s">
+      <c r="G157" s="5" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="158" ht="49.7" spans="1:7">
+    <row r="158" ht="62.15" spans="1:7">
       <c r="A158" s="3">
-        <v>1313</v>
+        <v>1265</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>24</v>
+        <v>314</v>
       </c>
       <c r="D158" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F158" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="E158" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F158" s="5" t="s">
+      <c r="G158" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="G158" s="6" t="s">
+    </row>
+    <row r="159" ht="62.15" spans="1:7">
+      <c r="A159" s="3">
+        <v>1266</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F159" s="7" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="159" ht="49.7" spans="1:7">
-      <c r="A159" s="3">
-        <v>1317</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F159" s="5" t="s">
+      <c r="G159" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G159" s="6" t="s">
+    </row>
+    <row r="160" ht="62.15" spans="1:7">
+      <c r="A160" s="3">
+        <v>1267</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F160" s="7" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="160" ht="49.7" spans="1:7">
-      <c r="A160" s="3">
-        <v>1318</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F160" s="5" t="s">
+      <c r="G160" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="G160" s="6" t="s">
+    </row>
+    <row r="161" ht="62.15" spans="1:7">
+      <c r="A161" s="3">
+        <v>1268</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F161" s="7" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="161" ht="49.7" spans="1:7">
-      <c r="A161" s="3">
-        <v>1319</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D161" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F161" s="5" t="s">
+      <c r="G161" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="G161" s="6" t="s">
+    </row>
+    <row r="162" ht="74.55" spans="1:7">
+      <c r="A162" s="3">
+        <v>1269</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F162" s="7" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="162" ht="62.15" spans="1:7">
-      <c r="A162" s="3">
-        <v>1320</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F162" s="5" t="s">
+      <c r="G162" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="G162" s="6" t="s">
+    </row>
+    <row r="163" ht="74.55" spans="1:7">
+      <c r="A163" s="3">
+        <v>1270</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F163" s="7" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="163" ht="49.7" spans="1:7">
-      <c r="A163" s="3">
-        <v>1321</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F163" s="5" t="s">
+      <c r="G163" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="G163" s="6" t="s">
+    </row>
+    <row r="164" ht="62.15" spans="1:7">
+      <c r="A164" s="3">
+        <v>1272</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F164" s="7" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="164" ht="49.7" spans="1:7">
-      <c r="A164" s="3">
-        <v>2144</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" s="4" t="s">
+      <c r="G164" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="D164" s="4" t="s">
+    </row>
+    <row r="165" ht="62.15" spans="1:7">
+      <c r="A165" s="3">
+        <v>1273</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F165" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="E164" s="4" t="s">
+      <c r="G165" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="F164" s="6" t="s">
+    </row>
+    <row r="166" ht="62.15" spans="1:7">
+      <c r="A166" s="3">
+        <v>1274</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F166" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="G164" s="6" t="s">
+      <c r="G166" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="165" ht="74.55" spans="1:7">
-      <c r="A165" s="3">
-        <v>2250</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D165" s="4" t="s">
+    <row r="167" ht="62.15" spans="1:7">
+      <c r="A167" s="3">
+        <v>1275</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F167" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="E165" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F165" s="5" t="s">
+      <c r="G167" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="G165" s="6" t="s">
+    </row>
+    <row r="168" ht="62.15" spans="1:7">
+      <c r="A168" s="3">
+        <v>1276</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F168" s="7" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="166" ht="74.55" spans="1:7">
-      <c r="A166" s="3">
-        <v>2251</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F166" s="5" t="s">
+      <c r="G168" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="G166" s="6" t="s">
+    </row>
+    <row r="169" ht="62.15" spans="1:7">
+      <c r="A169" s="3">
+        <v>1277</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F169" s="7" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="167" ht="74.55" spans="1:7">
-      <c r="A167" s="3">
-        <v>2252</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D167" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F167" s="5" t="s">
+      <c r="G169" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="G167" s="6" t="s">
+    </row>
+    <row r="170" ht="62.15" spans="1:7">
+      <c r="A170" s="3">
+        <v>1278</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F170" s="7" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="168" ht="74.55" spans="1:7">
-      <c r="A168" s="3">
-        <v>2253</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F168" s="5" t="s">
+      <c r="G170" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="G168" s="6" t="s">
+    </row>
+    <row r="171" ht="74.55" spans="1:7">
+      <c r="A171" s="3">
+        <v>1279</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F171" s="7" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="169" ht="87" spans="1:7">
-      <c r="A169" s="3">
-        <v>2254</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D169" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F169" s="5" t="s">
+      <c r="G171" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="G169" s="6" t="s">
+    </row>
+    <row r="172" ht="74.55" spans="1:7">
+      <c r="A172" s="3">
+        <v>1280</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F172" s="7" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="170" ht="87" spans="1:7">
-      <c r="A170" s="3">
-        <v>2255</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F170" s="5" t="s">
+      <c r="G172" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="G170" s="6" t="s">
+    </row>
+    <row r="173" ht="62.15" spans="1:7">
+      <c r="A173" s="3">
+        <v>1281</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F173" s="7" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="171" ht="87" spans="1:7">
-      <c r="A171" s="3">
-        <v>2256</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E171" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F171" s="5" t="s">
+      <c r="G173" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="G171" s="6" t="s">
+    </row>
+    <row r="174" ht="62.15" spans="1:7">
+      <c r="A174" s="3">
+        <v>1282</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F174" s="7" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="172" ht="87" spans="1:7">
-      <c r="A172" s="3">
-        <v>2257</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F172" s="5" t="s">
+      <c r="G174" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="G172" s="6" t="s">
+    </row>
+    <row r="175" ht="62.15" spans="1:7">
+      <c r="A175" s="3">
+        <v>1283</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="173" ht="74.55" spans="1:7">
-      <c r="A173" s="3">
-        <v>2258</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D173" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F173" s="5" t="s">
+      <c r="E175" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="G173" s="6" t="s">
+      <c r="G175" s="5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="174" ht="74.55" spans="1:7">
-      <c r="A174" s="3">
-        <v>2259</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F174" s="5" t="s">
+    <row r="176" ht="62.15" spans="1:7">
+      <c r="A176" s="3">
+        <v>1284</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="G174" s="6" t="s">
+      <c r="G176" s="5" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="175" ht="74.55" spans="1:7">
-      <c r="A175" s="3">
-        <v>2260</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="G175" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="176" ht="74.55" spans="1:7">
-      <c r="A176" s="3">
-        <v>2261</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D176" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="G176" s="6" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="177" ht="62.15" spans="1:7">
       <c r="A177" s="3">
-        <v>2270</v>
+        <v>1285</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D177" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="178" ht="74.55" spans="1:7">
+      <c r="A178" s="3">
+        <v>1286</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="179" ht="74.55" spans="1:7">
+      <c r="A179" s="3">
+        <v>1287</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="E177" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F177" s="5" t="s">
+      <c r="G179" s="5" t="s">
         <v>407</v>
-      </c>
-      <c r="G177" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="178" ht="62.15" spans="1:7">
-      <c r="A178" s="3">
-        <v>2271</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E178" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="G178" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="179" ht="62.15" spans="1:7">
-      <c r="A179" s="3">
-        <v>2272</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E179" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="G179" s="6" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="180" ht="62.15" spans="1:7">
       <c r="A180" s="3">
-        <v>2273</v>
+        <v>1288</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="G180" s="6" t="s">
-        <v>414</v>
+        <v>10</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="181" ht="62.15" spans="1:7">
       <c r="A181" s="3">
-        <v>2274</v>
+        <v>1289</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>416</v>
+        <v>10</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="182" ht="62.15" spans="1:7">
       <c r="A182" s="3">
-        <v>2275</v>
+        <v>1293</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="G182" s="6" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="183" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="183" ht="74.55" spans="1:7">
       <c r="A183" s="3">
-        <v>2276</v>
+        <v>1294</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="G183" s="6" t="s">
-        <v>420</v>
+        <v>10</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="184" ht="62.15" spans="1:7">
       <c r="A184" s="3">
-        <v>2277</v>
+        <v>1297</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="G184" s="6" t="s">
-        <v>422</v>
+        <v>10</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G184" s="5" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="185" ht="62.15" spans="1:7">
       <c r="A185" s="3">
-        <v>2278</v>
+        <v>1298</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="G185" s="6" t="s">
-        <v>424</v>
+        <v>10</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="186" ht="62.15" spans="1:7">
       <c r="A186" s="3">
-        <v>2279</v>
+        <v>1299</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="G186" s="6" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="187" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="187" ht="74.55" spans="1:7">
       <c r="A187" s="3">
-        <v>2280</v>
+        <v>1300</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="G187" s="6" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="188" ht="62.15" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="188" ht="74.55" spans="1:7">
       <c r="A188" s="3">
-        <v>2281</v>
+        <v>1301</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="G188" s="6" t="s">
-        <v>422</v>
+        <v>10</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="189" ht="62.15" spans="1:7">
       <c r="A189" s="3">
-        <v>2310</v>
+        <v>1302</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F189" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G189" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F189" s="7" t="s">
         <v>427</v>
+      </c>
+      <c r="G189" s="5" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="190" ht="62.15" spans="1:7">
       <c r="A190" s="3">
-        <v>2311</v>
+        <v>1303</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="G190" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F190" s="7" t="s">
         <v>429</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="191" ht="62.15" spans="1:7">
       <c r="A191" s="3">
-        <v>2312</v>
+        <v>1307</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="G191" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" s="7" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="192" ht="62.15" spans="1:7">
+      <c r="G191" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="192" ht="49.7" spans="1:7">
       <c r="A192" s="3">
-        <v>2575</v>
+        <v>1313</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="E192" s="4"/>
-      <c r="F192" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="G192" s="6" t="s">
+      <c r="E192" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="7" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="193" ht="62.15" spans="1:7">
+      <c r="G192" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="193" ht="49.7" spans="1:7">
       <c r="A193" s="3">
-        <v>2592</v>
+        <v>1317</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>435</v>
+        <v>45</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F193" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F193" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="G193" s="6" t="s">
+      <c r="G193" s="5" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="194" ht="62.15" spans="1:7">
+    <row r="194" ht="49.7" spans="1:7">
       <c r="A194" s="3">
-        <v>2603</v>
+        <v>1318</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D194" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F194" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="E194" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F194" s="5" t="s">
+      <c r="G194" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="G194" s="6" t="s">
+    </row>
+    <row r="195" ht="49.7" spans="1:7">
+      <c r="A195" s="3">
+        <v>1319</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="7" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="195" ht="62.15" spans="1:7">
-      <c r="A195" s="3">
-        <v>2606</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D195" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F195" s="5" t="s">
+      <c r="G195" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="G195" s="6" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="196" ht="62.15" spans="1:7">
       <c r="A196" s="3">
-        <v>2607</v>
+        <v>1320</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F196" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="G196" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="G196" s="6" t="s">
+    </row>
+    <row r="197" ht="49.7" spans="1:7">
+      <c r="A197" s="3">
+        <v>1321</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F197" s="7" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="197" ht="62.15" spans="1:7">
-      <c r="A197" s="3">
-        <v>2608</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E197" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F197" s="5" t="s">
+      <c r="G197" s="5" t="s">
         <v>445</v>
-      </c>
-      <c r="G197" s="6" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="198" ht="49.7" spans="1:7">
       <c r="A198" s="3">
+        <v>2144</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="199" ht="74.55" spans="1:7">
+      <c r="A199" s="3">
+        <v>2250</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="200" ht="74.55" spans="1:7">
+      <c r="A200" s="3">
+        <v>2251</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G200" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="201" ht="74.55" spans="1:7">
+      <c r="A201" s="3">
+        <v>2252</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="202" ht="74.55" spans="1:7">
+      <c r="A202" s="3">
+        <v>2253</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="203" ht="87" spans="1:7">
+      <c r="A203" s="3">
+        <v>2254</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="204" ht="87" spans="1:7">
+      <c r="A204" s="3">
+        <v>2255</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G204" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="205" ht="87" spans="1:7">
+      <c r="A205" s="3">
+        <v>2256</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="206" ht="87" spans="1:7">
+      <c r="A206" s="3">
+        <v>2257</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="G206" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="207" ht="74.55" spans="1:7">
+      <c r="A207" s="3">
+        <v>2258</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G207" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="208" ht="74.55" spans="1:7">
+      <c r="A208" s="3">
+        <v>2259</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="G208" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="209" ht="74.55" spans="1:7">
+      <c r="A209" s="3">
+        <v>2260</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="G209" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="210" ht="74.55" spans="1:7">
+      <c r="A210" s="3">
+        <v>2261</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="G210" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="211" ht="62.15" spans="1:7">
+      <c r="A211" s="3">
+        <v>2270</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F211" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="212" ht="62.15" spans="1:7">
+      <c r="A212" s="3">
+        <v>2271</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G212" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="213" ht="62.15" spans="1:7">
+      <c r="A213" s="3">
+        <v>2272</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="214" ht="62.15" spans="1:7">
+      <c r="A214" s="3">
+        <v>2273</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G214" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="215" ht="62.15" spans="1:7">
+      <c r="A215" s="3">
+        <v>2274</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E215" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="G215" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="216" ht="62.15" spans="1:7">
+      <c r="A216" s="3">
+        <v>2275</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="G216" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="217" ht="62.15" spans="1:7">
+      <c r="A217" s="3">
+        <v>2276</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E217" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="G217" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="218" ht="62.15" spans="1:7">
+      <c r="A218" s="3">
+        <v>2277</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G218" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="219" ht="62.15" spans="1:7">
+      <c r="A219" s="3">
+        <v>2278</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E219" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="G219" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="220" ht="62.15" spans="1:7">
+      <c r="A220" s="3">
+        <v>2279</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E220" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="G220" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="221" ht="62.15" spans="1:7">
+      <c r="A221" s="3">
+        <v>2280</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E221" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="G221" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="222" ht="62.15" spans="1:7">
+      <c r="A222" s="3">
+        <v>2281</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G222" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="223" ht="62.15" spans="1:7">
+      <c r="A223" s="3">
+        <v>2310</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="224" ht="62.15" spans="1:7">
+      <c r="A224" s="3">
+        <v>2311</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="225" ht="62.15" spans="1:7">
+      <c r="A225" s="3">
+        <v>2312</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E225" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="226" ht="62.15" spans="1:7">
+      <c r="A226" s="3">
+        <v>2575</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="E226" s="4"/>
+      <c r="F226" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="227" ht="62.15" spans="1:7">
+      <c r="A227" s="3">
+        <v>2592</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="E227" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="228" ht="62.15" spans="1:7">
+      <c r="A228" s="3">
+        <v>2603</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E228" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="G228" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="229" ht="62.15" spans="1:7">
+      <c r="A229" s="3">
+        <v>2606</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E229" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="230" ht="62.15" spans="1:7">
+      <c r="A230" s="3">
+        <v>2607</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="G230" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="231" ht="62.15" spans="1:7">
+      <c r="A231" s="3">
+        <v>2608</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E231" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="232" ht="49.7" spans="1:7">
+      <c r="A232" s="3">
         <v>2609</v>
       </c>
-      <c r="B198" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="G198" s="6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="199" ht="49.7" spans="1:7">
-      <c r="A199" s="3">
+      <c r="B232" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E232" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="233" ht="49.7" spans="1:7">
+      <c r="A233" s="3">
         <v>2610</v>
       </c>
-      <c r="B199" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D199" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E199" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G199" s="6" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="200" ht="49.7" spans="1:7">
-      <c r="A200" s="3">
+      <c r="B233" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E233" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="234" ht="49.7" spans="1:7">
+      <c r="A234" s="3">
         <v>2611</v>
       </c>
-      <c r="B200" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D200" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="G200" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="201" ht="49.7" spans="1:7">
-      <c r="A201" s="3">
+      <c r="B234" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E234" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="235" ht="49.7" spans="1:7">
+      <c r="A235" s="3">
         <v>2612</v>
       </c>
-      <c r="B201" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D201" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E201" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="G201" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="202" ht="49.7" spans="1:7">
-      <c r="A202" s="3">
+      <c r="B235" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E235" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="236" ht="49.7" spans="1:7">
+      <c r="A236" s="3">
         <v>2613</v>
       </c>
-      <c r="B202" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D202" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E202" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F202" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="G202" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="203" ht="62.15" spans="1:7">
-      <c r="A203" s="3">
+      <c r="B236" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E236" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="G236" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="237" ht="62.15" spans="1:7">
+      <c r="A237" s="3">
         <v>2614</v>
       </c>
-      <c r="B203" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D203" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E203" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F203" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="G203" s="6" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="204" ht="62.15" spans="1:7">
-      <c r="A204" s="3">
+      <c r="B237" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E237" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="238" ht="62.15" spans="1:7">
+      <c r="A238" s="3">
         <v>2615</v>
       </c>
-      <c r="B204" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D204" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E204" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="G204" s="6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="205" ht="62.15" spans="1:7">
-      <c r="A205" s="3">
+      <c r="B238" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E238" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="239" ht="62.15" spans="1:7">
+      <c r="A239" s="3">
         <v>2616</v>
       </c>
-      <c r="B205" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D205" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E205" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F205" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="G205" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="206" ht="62.15" spans="1:7">
-      <c r="A206" s="3">
+      <c r="B239" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E239" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="240" ht="62.15" spans="1:7">
+      <c r="A240" s="3">
         <v>2617</v>
       </c>
-      <c r="B206" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E206" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="G206" s="6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7">
-      <c r="A207" s="8"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="10"/>
-      <c r="G207" s="11"/>
-    </row>
-    <row r="208" spans="1:7">
-      <c r="A208" s="8"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="10"/>
-      <c r="G208" s="11"/>
-    </row>
-    <row r="209" spans="1:7">
-      <c r="A209" s="8"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="10"/>
-      <c r="G209" s="11"/>
-    </row>
-    <row r="210" spans="1:7">
-      <c r="A210" s="8"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="10"/>
-      <c r="G210" s="11"/>
-    </row>
-    <row r="211" spans="1:7">
-      <c r="A211" s="8"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
-      <c r="D211" s="9"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="10"/>
-      <c r="G211" s="11"/>
-    </row>
-    <row r="212" spans="1:7">
-      <c r="A212" s="8"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="9"/>
-      <c r="D212" s="9"/>
-      <c r="E212" s="9"/>
-      <c r="F212" s="10"/>
-      <c r="G212" s="11"/>
-    </row>
-    <row r="213" spans="1:7">
-      <c r="A213" s="8"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
-      <c r="D213" s="9"/>
-      <c r="E213" s="9"/>
-      <c r="F213" s="10"/>
-      <c r="G213" s="11"/>
-    </row>
-    <row r="214" spans="1:7">
-      <c r="A214" s="8"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
-      <c r="D214" s="9"/>
-      <c r="E214" s="9"/>
-      <c r="F214" s="10"/>
-      <c r="G214" s="11"/>
-    </row>
-    <row r="215" spans="1:7">
-      <c r="A215" s="8"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="9"/>
-      <c r="E215" s="9"/>
-      <c r="F215" s="10"/>
-      <c r="G215" s="11"/>
-    </row>
-    <row r="216" spans="1:7">
-      <c r="A216" s="8"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="9"/>
-      <c r="D216" s="9"/>
-      <c r="E216" s="9"/>
-      <c r="F216" s="10"/>
-      <c r="G216" s="11"/>
-    </row>
-    <row r="217" spans="1:7">
-      <c r="A217" s="8"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="10"/>
-      <c r="G217" s="11"/>
-    </row>
-    <row r="218" spans="1:7">
-      <c r="A218" s="8"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="10"/>
-      <c r="G218" s="11"/>
-    </row>
-    <row r="219" spans="1:7">
-      <c r="A219" s="8"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="10"/>
-      <c r="G219" s="11"/>
-    </row>
-    <row r="220" spans="1:7">
-      <c r="A220" s="8"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="10"/>
-      <c r="G220" s="11"/>
-    </row>
-    <row r="221" spans="1:7">
-      <c r="A221" s="8"/>
-      <c r="B221" s="9"/>
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
-      <c r="F221" s="10"/>
-      <c r="G221" s="11"/>
-    </row>
-    <row r="222" spans="1:7">
-      <c r="A222" s="8"/>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="10"/>
-      <c r="G222" s="11"/>
-    </row>
-    <row r="223" spans="1:7">
-      <c r="A223" s="8"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
-      <c r="E223" s="9"/>
-      <c r="F223" s="10"/>
-      <c r="G223" s="11"/>
-    </row>
-    <row r="224" spans="1:7">
-      <c r="A224" s="8"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
-      <c r="D224" s="9"/>
-      <c r="E224" s="9"/>
-      <c r="F224" s="10"/>
-      <c r="G224" s="11"/>
-    </row>
-    <row r="225" spans="1:7">
-      <c r="A225" s="8"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
-      <c r="E225" s="9"/>
-      <c r="F225" s="10"/>
-      <c r="G225" s="11"/>
-    </row>
-    <row r="226" spans="1:7">
-      <c r="A226" s="8"/>
-      <c r="B226" s="9"/>
-      <c r="C226" s="9"/>
-      <c r="D226" s="9"/>
-      <c r="E226" s="9"/>
-      <c r="F226" s="10"/>
-      <c r="G226" s="11"/>
-    </row>
-    <row r="227" spans="1:7">
-      <c r="A227" s="8"/>
-      <c r="B227" s="9"/>
-      <c r="C227" s="9"/>
-      <c r="D227" s="9"/>
-      <c r="E227" s="9"/>
-      <c r="F227" s="10"/>
-      <c r="G227" s="11"/>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228" s="8"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="9"/>
-      <c r="F228" s="10"/>
-      <c r="G228" s="11"/>
-    </row>
-    <row r="229" spans="1:7">
-      <c r="A229" s="8"/>
-      <c r="B229" s="9"/>
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="F229" s="10"/>
-      <c r="G229" s="11"/>
-    </row>
-    <row r="230" spans="1:7">
-      <c r="A230" s="8"/>
-      <c r="B230" s="9"/>
-      <c r="C230" s="9"/>
-      <c r="D230" s="9"/>
-      <c r="E230" s="9"/>
-      <c r="F230" s="10"/>
-      <c r="G230" s="11"/>
-    </row>
-    <row r="231" spans="1:7">
-      <c r="A231" s="8"/>
-      <c r="B231" s="9"/>
-      <c r="C231" s="9"/>
-      <c r="D231" s="9"/>
-      <c r="E231" s="9"/>
-      <c r="F231" s="10"/>
-      <c r="G231" s="11"/>
-    </row>
-    <row r="232" spans="1:7">
-      <c r="A232" s="8"/>
-      <c r="B232" s="9"/>
-      <c r="C232" s="9"/>
-      <c r="D232" s="9"/>
-      <c r="E232" s="9"/>
-      <c r="F232" s="10"/>
-      <c r="G232" s="11"/>
-    </row>
-    <row r="233" spans="1:7">
-      <c r="A233" s="8"/>
-      <c r="B233" s="9"/>
-      <c r="C233" s="9"/>
-      <c r="D233" s="9"/>
-      <c r="E233" s="9"/>
-      <c r="F233" s="10"/>
-      <c r="G233" s="11"/>
-    </row>
-    <row r="234" spans="1:7">
-      <c r="A234" s="8"/>
-      <c r="B234" s="9"/>
-      <c r="C234" s="9"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="9"/>
-      <c r="F234" s="10"/>
-      <c r="G234" s="11"/>
-    </row>
-    <row r="235" spans="1:7">
-      <c r="A235" s="8"/>
-      <c r="B235" s="9"/>
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="F235" s="10"/>
-      <c r="G235" s="11"/>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236" s="8"/>
-      <c r="B236" s="9"/>
-      <c r="C236" s="9"/>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="F236" s="10"/>
-      <c r="G236" s="11"/>
-    </row>
-    <row r="237" spans="1:7">
-      <c r="A237" s="8"/>
-      <c r="B237" s="9"/>
-      <c r="C237" s="9"/>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="10"/>
-      <c r="G237" s="11"/>
-    </row>
-    <row r="238" spans="1:7">
-      <c r="A238" s="8"/>
-      <c r="B238" s="9"/>
-      <c r="C238" s="9"/>
-      <c r="D238" s="9"/>
-      <c r="E238" s="9"/>
-      <c r="F238" s="10"/>
-      <c r="G238" s="11"/>
-    </row>
-    <row r="239" spans="1:7">
-      <c r="A239" s="8"/>
-      <c r="B239" s="9"/>
-      <c r="C239" s="9"/>
-      <c r="D239" s="9"/>
-      <c r="E239" s="9"/>
-      <c r="F239" s="10"/>
-      <c r="G239" s="11"/>
-    </row>
-    <row r="240" spans="1:7">
-      <c r="A240" s="8"/>
-      <c r="B240" s="9"/>
-      <c r="C240" s="9"/>
-      <c r="D240" s="9"/>
-      <c r="E240" s="9"/>
-      <c r="F240" s="10"/>
-      <c r="G240" s="11"/>
+      <c r="B240" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E240" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>534</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/创新支撑系统-功能点走查记录.xlsx
+++ b/创新支撑系统-功能点走查记录.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="596">
   <si>
     <t>序号</t>
   </si>
@@ -178,15 +178,87 @@
     <t>对手动通知信息管理进行配置管理操作</t>
   </si>
   <si>
+    <t>工单中心</t>
+  </si>
+  <si>
+    <t>工单管理运营侧</t>
+  </si>
+  <si>
+    <t>我的代办</t>
+  </si>
+  <si>
+    <t>我的代办管理</t>
+  </si>
+  <si>
+    <t>对我的代办管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送我的工单</t>
+  </si>
+  <si>
+    <t>抄送工单统计管理</t>
+  </si>
+  <si>
+    <t>对抄送工单统计管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>办件中心</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>待阅工单事项统计配置信息管理</t>
+  </si>
+  <si>
+    <t>对待阅工单事项统计配置信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>待阅工单事项展示规则配置信息管理</t>
+  </si>
+  <si>
+    <t>对待阅工单事项展示规则配置信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>待阅工单定时器配置信息管理</t>
+  </si>
+  <si>
+    <t>对待阅工单定时器配置信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单抄送管理</t>
+  </si>
+  <si>
+    <t>默认抄送规则配置信息管理</t>
+  </si>
+  <si>
+    <t>对默认抄送规则配置信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>默认抄送记录信息管理</t>
+  </si>
+  <si>
+    <t>对默认抄送记录信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>自定义抄送设置信息管理</t>
+  </si>
+  <si>
+    <t>对自定义抄送设置信息管理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>自定义抄送记录信息管理</t>
+  </si>
+  <si>
+    <t>对自定义抄送记录信息管理进行配置管理操作</t>
+  </si>
+  <si>
     <t>系统管理</t>
   </si>
   <si>
     <t>基础设置</t>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
     <t>账号安全设置管理</t>
   </si>
   <si>
@@ -1372,12 +1444,6 @@
     <t>对手动通知用户进行配置管理操作</t>
   </si>
   <si>
-    <t>工单中心</t>
-  </si>
-  <si>
-    <t>工单管理运营侧</t>
-  </si>
-  <si>
     <t>工单评价管理</t>
   </si>
   <si>
@@ -1387,7 +1453,103 @@
     <t>对工单评价新增进行配置管理操作</t>
   </si>
   <si>
-    <t>办件中心</t>
+    <t>工单类型管理</t>
+  </si>
+  <si>
+    <t>工单类型查询</t>
+  </si>
+  <si>
+    <t>对工单类型查询进行配置管理操作</t>
+  </si>
+  <si>
+    <t>我的代办工单查询</t>
+  </si>
+  <si>
+    <t>对我的代办工单查询进行配置管理操作</t>
+  </si>
+  <si>
+    <t>我的代办工单条件重置</t>
+  </si>
+  <si>
+    <t>对我的代办工单条件重置进行配置管理操作</t>
+  </si>
+  <si>
+    <t>我的代办工单详情</t>
+  </si>
+  <si>
+    <t>对我的代办工单详情进行配置管理操作</t>
+  </si>
+  <si>
+    <t>我的代办工单办理</t>
+  </si>
+  <si>
+    <t>对我的代办工单办理进行配置管理操作</t>
+  </si>
+  <si>
+    <t>我的代办工单移交</t>
+  </si>
+  <si>
+    <t>对我的代办工单移交进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送我的工单详情查看</t>
+  </si>
+  <si>
+    <t>对抄送我的工单详情查看进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送我的工单详情评分</t>
+  </si>
+  <si>
+    <t>对抄送我的工单详情评分进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送我的工单详情附件上传</t>
+  </si>
+  <si>
+    <t>对抄送我的工单详情附件上传进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送工单统计新增</t>
+  </si>
+  <si>
+    <t>对抄送工单统计新增进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送工单统计修改</t>
+  </si>
+  <si>
+    <t>对抄送工单统计修改进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送工单统计删除</t>
+  </si>
+  <si>
+    <t>对抄送工单统计删除进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送工单统计查询</t>
+  </si>
+  <si>
+    <t>对抄送工单统计查询进行配置管理操作</t>
+  </si>
+  <si>
+    <t>抄送工单统计转发</t>
+  </si>
+  <si>
+    <t>对抄送工单统计转发进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单管理客户侧—pc端</t>
+  </si>
+  <si>
+    <t>我的工单管理</t>
+  </si>
+  <si>
+    <t>我的工单排序</t>
+  </si>
+  <si>
+    <t>对我的工单排序进行配置管理操作</t>
   </si>
   <si>
     <t>待阅工单事项统计配置信息新增</t>
@@ -1462,7 +1624,28 @@
     <t>对待阅工单定时器配置信息查询进行配置管理操作</t>
   </si>
   <si>
-    <t>工单抄送管理</t>
+    <t>工单信息新增</t>
+  </si>
+  <si>
+    <t>对工单信息新增进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单信息修改</t>
+  </si>
+  <si>
+    <t>对工单信息修改进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单信息删除</t>
+  </si>
+  <si>
+    <t>对工单信息删除进行配置管理操作</t>
+  </si>
+  <si>
+    <t>工单信息查询</t>
+  </si>
+  <si>
+    <t>对工单信息查询进行配置管理操作</t>
   </si>
   <si>
     <t>默认抄送记录信息新增</t>
@@ -2888,7 +3071,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" ht="24.85" spans="1:7">
@@ -3190,9 +3373,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="62.15" spans="1:7">
+    <row r="14" ht="49.7" spans="1:7">
       <c r="A14" s="3">
-        <v>428</v>
+        <v>311</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>7</v>
@@ -3206,7 +3389,7 @@
       <c r="E14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="G14" s="5" t="s">
@@ -3215,7 +3398,7 @@
     </row>
     <row r="15" ht="62.15" spans="1:7">
       <c r="A15" s="3">
-        <v>429</v>
+        <v>313</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
@@ -3227,18 +3410,18 @@
         <v>49</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" ht="49.7" spans="1:7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" ht="74.55" spans="1:7">
       <c r="A16" s="3">
-        <v>430</v>
+        <v>332</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>7</v>
@@ -3247,21 +3430,21 @@
         <v>48</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" ht="62.15" spans="1:7">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" ht="87" spans="1:7">
       <c r="A17" s="3">
-        <v>431</v>
+        <v>333</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>7</v>
@@ -3270,58 +3453,58 @@
         <v>48</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" ht="74.55" spans="1:7">
+      <c r="A18" s="3">
+        <v>334</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" ht="49.7" spans="1:7">
-      <c r="A18" s="3">
-        <v>436</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" ht="62.15" spans="1:7">
+    <row r="19" ht="74.55" spans="1:7">
       <c r="A19" s="3">
-        <v>438</v>
+        <v>335</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="5" t="s">
@@ -3330,19 +3513,19 @@
     </row>
     <row r="20" ht="62.15" spans="1:7">
       <c r="A20" s="3">
-        <v>439</v>
+        <v>337</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>67</v>
@@ -3353,21 +3536,21 @@
     </row>
     <row r="21" ht="62.15" spans="1:7">
       <c r="A21" s="3">
-        <v>440</v>
+        <v>338</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="5" t="s">
@@ -3376,21 +3559,21 @@
     </row>
     <row r="22" ht="62.15" spans="1:7">
       <c r="A22" s="3">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="5" t="s">
@@ -3399,605 +3582,605 @@
     </row>
     <row r="23" ht="62.15" spans="1:7">
       <c r="A23" s="3">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" ht="62.15" spans="1:7">
       <c r="A24" s="3">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" ht="62.15" spans="1:7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" ht="49.7" spans="1:7">
       <c r="A25" s="3">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>78</v>
+        <v>57</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" ht="62.15" spans="1:7">
       <c r="A26" s="3">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>81</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" ht="62.15" spans="1:7">
+    <row r="27" ht="49.7" spans="1:7">
       <c r="A27" s="3">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="62.15" spans="1:7">
       <c r="A28" s="3">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="62.15" spans="1:7">
       <c r="A29" s="3">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" ht="62.15" spans="1:7">
       <c r="A30" s="3">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" ht="62.15" spans="1:7">
       <c r="A31" s="3">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" ht="62.15" spans="1:7">
       <c r="A32" s="3">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" ht="62.15" spans="1:7">
       <c r="A33" s="3">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" ht="62.15" spans="1:7">
       <c r="A34" s="3">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" ht="62.15" spans="1:7">
       <c r="A35" s="3">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" ht="62.15" spans="1:7">
       <c r="A36" s="3">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" ht="62.15" spans="1:7">
       <c r="A37" s="3">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" ht="62.15" spans="1:7">
       <c r="A38" s="3">
+        <v>458</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" ht="62.15" spans="1:7">
+      <c r="A39" s="3">
+        <v>459</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" ht="62.15" spans="1:7">
+      <c r="A40" s="3">
+        <v>463</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" ht="62.15" spans="1:7">
+      <c r="A41" s="3">
+        <v>464</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" ht="62.15" spans="1:7">
+      <c r="A42" s="3">
+        <v>465</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" ht="62.15" spans="1:7">
+      <c r="A43" s="3">
+        <v>469</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" ht="62.15" spans="1:7">
+      <c r="A44" s="3">
+        <v>470</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" ht="62.15" spans="1:7">
+      <c r="A45" s="3">
+        <v>471</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" ht="62.15" spans="1:7">
+      <c r="A46" s="3">
+        <v>475</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" ht="62.15" spans="1:7">
+      <c r="A47" s="3">
         <v>476</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" ht="49.7" spans="1:7">
-      <c r="A39" s="3">
+      <c r="B47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" ht="49.7" spans="1:7">
+      <c r="A48" s="3">
         <v>477</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" ht="49.7" spans="1:7">
-      <c r="A40" s="3">
+      <c r="B48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" ht="49.7" spans="1:7">
+      <c r="A49" s="3">
         <v>483</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" ht="49.7" spans="1:7">
-      <c r="A41" s="3">
-        <v>484</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" ht="49.7" spans="1:7">
-      <c r="A42" s="3">
-        <v>485</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" ht="49.7" spans="1:7">
-      <c r="A43" s="3">
-        <v>486</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" ht="49.7" spans="1:7">
-      <c r="A44" s="3">
-        <v>487</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="45" ht="49.7" spans="1:7">
-      <c r="A45" s="3">
-        <v>532</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" ht="49.7" spans="1:7">
-      <c r="A46" s="3">
-        <v>533</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" ht="49.7" spans="1:7">
-      <c r="A47" s="3">
-        <v>534</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="48" ht="62.15" spans="1:7">
-      <c r="A48" s="3">
-        <v>535</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" ht="62.15" spans="1:7">
-      <c r="A49" s="3">
-        <v>536</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>7</v>
@@ -4006,21 +4189,21 @@
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>131</v>
+        <v>10</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" ht="49.7" spans="1:7">
       <c r="A50" s="3">
-        <v>537</v>
+        <v>484</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>7</v>
@@ -4029,21 +4212,21 @@
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>133</v>
+        <v>10</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" ht="49.7" spans="1:7">
       <c r="A51" s="3">
-        <v>538</v>
+        <v>485</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>7</v>
@@ -4052,21 +4235,21 @@
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>135</v>
+        <v>10</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" ht="49.7" spans="1:7">
       <c r="A52" s="3">
-        <v>539</v>
+        <v>486</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>7</v>
@@ -4075,21 +4258,21 @@
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>137</v>
+        <v>10</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" ht="49.7" spans="1:7">
       <c r="A53" s="3">
-        <v>540</v>
+        <v>487</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>7</v>
@@ -4098,21 +4281,21 @@
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>139</v>
+        <v>10</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" ht="49.7" spans="1:7">
       <c r="A54" s="3">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>7</v>
@@ -4124,18 +4307,18 @@
         <v>12</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="55" ht="62.15" spans="1:7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" ht="49.7" spans="1:7">
       <c r="A55" s="3">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>7</v>
@@ -4147,18 +4330,18 @@
         <v>12</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" ht="62.15" spans="1:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" ht="49.7" spans="1:7">
       <c r="A56" s="3">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>7</v>
@@ -4170,18 +4353,18 @@
         <v>12</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="57" ht="49.7" spans="1:7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" ht="62.15" spans="1:7">
       <c r="A57" s="3">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>7</v>
@@ -4193,18 +4376,18 @@
         <v>12</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="58" ht="49.7" spans="1:7">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" ht="62.15" spans="1:7">
       <c r="A58" s="3">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>7</v>
@@ -4216,18 +4399,18 @@
         <v>12</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" ht="49.7" spans="1:7">
       <c r="A59" s="3">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>7</v>
@@ -4236,21 +4419,21 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" ht="49.7" spans="1:7">
       <c r="A60" s="3">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>7</v>
@@ -4259,21 +4442,21 @@
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" ht="49.7" spans="1:7">
       <c r="A61" s="3">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>7</v>
@@ -4282,21 +4465,21 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" ht="62.15" spans="1:7">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="62" ht="49.7" spans="1:7">
       <c r="A62" s="3">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>7</v>
@@ -4305,21 +4488,21 @@
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" ht="49.7" spans="1:7">
       <c r="A63" s="3">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>7</v>
@@ -4328,21 +4511,21 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="64" ht="49.7" spans="1:7">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" ht="62.15" spans="1:7">
       <c r="A64" s="3">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>7</v>
@@ -4351,21 +4534,21 @@
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="65" ht="49.7" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" ht="62.15" spans="1:7">
       <c r="A65" s="3">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>7</v>
@@ -4374,21 +4557,21 @@
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" ht="49.7" spans="1:7">
       <c r="A66" s="3">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>7</v>
@@ -4397,21 +4580,21 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="67" ht="49.7" spans="1:7">
       <c r="A67" s="3">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>7</v>
@@ -4420,21 +4603,21 @@
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" ht="49.7" spans="1:7">
       <c r="A68" s="3">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>7</v>
@@ -4449,15 +4632,15 @@
         <v>10</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" ht="49.7" spans="1:7">
       <c r="A69" s="3">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>7</v>
@@ -4472,15 +4655,15 @@
         <v>10</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" ht="49.7" spans="1:7">
       <c r="A70" s="3">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>7</v>
@@ -4495,15 +4678,15 @@
         <v>10</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="71" ht="49.7" spans="1:7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" ht="62.15" spans="1:7">
       <c r="A71" s="3">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>7</v>
@@ -4512,21 +4695,21 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F71" s="5" t="s">
-        <v>176</v>
+      <c r="F71" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72" ht="49.7" spans="1:7">
       <c r="A72" s="3">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>7</v>
@@ -4535,21 +4718,21 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>179</v>
+      <c r="F72" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="73" ht="62.15" spans="1:7">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" ht="49.7" spans="1:7">
       <c r="A73" s="3">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>7</v>
@@ -4558,21 +4741,21 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" ht="49.7" spans="1:7">
       <c r="A74" s="3">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>7</v>
@@ -4581,21 +4764,21 @@
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F74" s="5" t="s">
-        <v>184</v>
+      <c r="F74" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" ht="49.7" spans="1:7">
       <c r="A75" s="3">
-        <v>582</v>
+        <v>553</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>7</v>
@@ -4604,21 +4787,21 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F75" s="5" t="s">
-        <v>186</v>
+      <c r="F75" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" ht="49.7" spans="1:7">
       <c r="A76" s="3">
-        <v>597</v>
+        <v>554</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>7</v>
@@ -4627,53 +4810,53 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="77" ht="62.15" spans="1:7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" ht="49.7" spans="1:7">
       <c r="A77" s="3">
-        <v>601</v>
+        <v>555</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="78" ht="74.55" spans="1:7">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="78" ht="49.7" spans="1:7">
       <c r="A78" s="3">
-        <v>621</v>
+        <v>556</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>10</v>
@@ -4685,18 +4868,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" ht="74.55" spans="1:7">
+    <row r="79" ht="49.7" spans="1:7">
       <c r="A79" s="3">
-        <v>622</v>
+        <v>557</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>10</v>
@@ -4708,107 +4891,107 @@
         <v>198</v>
       </c>
     </row>
-    <row r="80" ht="74.55" spans="1:7">
+    <row r="80" ht="49.7" spans="1:7">
       <c r="A80" s="3">
-        <v>623</v>
+        <v>564</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>199</v>
+      <c r="F80" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="81" ht="74.55" spans="1:7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="81" ht="49.7" spans="1:7">
       <c r="A81" s="3">
-        <v>624</v>
+        <v>572</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>201</v>
+      <c r="F81" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G81" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="82" ht="62.15" spans="1:7">
+      <c r="A82" s="3">
+        <v>575</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="82" ht="87" spans="1:7">
-      <c r="A82" s="3">
-        <v>633</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" ht="62.15" spans="1:7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="83" ht="49.7" spans="1:7">
       <c r="A83" s="3">
-        <v>638</v>
+        <v>578</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>205</v>
+      <c r="F83" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" ht="49.7" spans="1:7">
       <c r="A84" s="3">
-        <v>639</v>
+        <v>582</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>207</v>
@@ -4816,246 +4999,246 @@
       <c r="E84" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>208</v>
+      <c r="F84" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" ht="49.7" spans="1:7">
       <c r="A85" s="3">
-        <v>640</v>
+        <v>597</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="86" ht="49.7" spans="1:7">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" ht="62.15" spans="1:7">
       <c r="A86" s="3">
+        <v>601</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" ht="74.55" spans="1:7">
+      <c r="A87" s="3">
+        <v>621</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="88" ht="74.55" spans="1:7">
+      <c r="A88" s="3">
+        <v>622</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="89" ht="74.55" spans="1:7">
+      <c r="A89" s="3">
+        <v>623</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="90" ht="74.55" spans="1:7">
+      <c r="A90" s="3">
+        <v>624</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="91" ht="87" spans="1:7">
+      <c r="A91" s="3">
+        <v>633</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="92" ht="62.15" spans="1:7">
+      <c r="A92" s="3">
+        <v>638</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93" ht="49.7" spans="1:7">
+      <c r="A93" s="3">
+        <v>639</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="94" ht="49.7" spans="1:7">
+      <c r="A94" s="3">
+        <v>640</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="95" ht="49.7" spans="1:7">
+      <c r="A95" s="3">
         <v>678</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="87" ht="49.7" spans="1:7">
-      <c r="A87" s="3">
-        <v>679</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" ht="49.7" spans="1:7">
-      <c r="A88" s="3">
-        <v>680</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="89" ht="62.15" spans="1:7">
-      <c r="A89" s="3">
-        <v>681</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="90" ht="62.15" spans="1:7">
-      <c r="A90" s="3">
-        <v>682</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="91" ht="49.7" spans="1:7">
-      <c r="A91" s="3">
-        <v>683</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="92" ht="49.7" spans="1:7">
-      <c r="A92" s="3">
-        <v>684</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="93" ht="62.15" spans="1:7">
-      <c r="A93" s="3">
-        <v>685</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="94" ht="62.15" spans="1:7">
-      <c r="A94" s="3">
-        <v>686</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="95" ht="62.15" spans="1:7">
-      <c r="A95" s="3">
-        <v>687</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>7</v>
@@ -5067,18 +5250,18 @@
         <v>29</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="96" ht="62.15" spans="1:7">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="96" ht="49.7" spans="1:7">
       <c r="A96" s="3">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>7</v>
@@ -5090,18 +5273,18 @@
         <v>29</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="97" ht="74.55" spans="1:7">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" ht="49.7" spans="1:7">
       <c r="A97" s="3">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>7</v>
@@ -5113,18 +5296,18 @@
         <v>29</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" ht="62.15" spans="1:7">
       <c r="A98" s="3">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>7</v>
@@ -5136,18 +5319,18 @@
         <v>29</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="99" ht="62.15" spans="1:7">
       <c r="A99" s="3">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>7</v>
@@ -5159,18 +5342,18 @@
         <v>29</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" ht="49.7" spans="1:7">
       <c r="A100" s="3">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>7</v>
@@ -5182,18 +5365,18 @@
         <v>29</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" ht="49.7" spans="1:7">
       <c r="A101" s="3">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>7</v>
@@ -5205,18 +5388,18 @@
         <v>29</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="102" ht="49.7" spans="1:7">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="102" ht="62.15" spans="1:7">
       <c r="A102" s="3">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>7</v>
@@ -5228,18 +5411,18 @@
         <v>29</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="103" ht="62.15" spans="1:7">
       <c r="A103" s="3">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>7</v>
@@ -5251,18 +5434,18 @@
         <v>29</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="104" ht="62.15" spans="1:7">
       <c r="A104" s="3">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>7</v>
@@ -5274,18 +5457,18 @@
         <v>29</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="105" ht="49.7" spans="1:7">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="105" ht="62.15" spans="1:7">
       <c r="A105" s="3">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>7</v>
@@ -5297,18 +5480,18 @@
         <v>29</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="106" ht="49.7" spans="1:7">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="106" ht="74.55" spans="1:7">
       <c r="A106" s="3">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>7</v>
@@ -5320,18 +5503,18 @@
         <v>29</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" ht="62.15" spans="1:7">
       <c r="A107" s="3">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>7</v>
@@ -5343,18 +5526,18 @@
         <v>29</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>254</v>
+        <v>33</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" ht="62.15" spans="1:7">
       <c r="A108" s="3">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>7</v>
@@ -5366,18 +5549,18 @@
         <v>29</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>254</v>
+        <v>33</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="109" ht="62.15" spans="1:7">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="109" ht="49.7" spans="1:7">
       <c r="A109" s="3">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>7</v>
@@ -5389,18 +5572,18 @@
         <v>29</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="110" ht="62.15" spans="1:7">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="110" ht="49.7" spans="1:7">
       <c r="A110" s="3">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>7</v>
@@ -5412,18 +5595,18 @@
         <v>29</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="111" ht="74.55" spans="1:7">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="111" ht="49.7" spans="1:7">
       <c r="A111" s="3">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>7</v>
@@ -5435,18 +5618,18 @@
         <v>29</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" ht="62.15" spans="1:7">
       <c r="A112" s="3">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>7</v>
@@ -5458,18 +5641,18 @@
         <v>29</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="113" ht="62.15" spans="1:7">
       <c r="A113" s="3">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>7</v>
@@ -5481,18 +5664,18 @@
         <v>29</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="114" ht="49.7" spans="1:7">
       <c r="A114" s="3">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>7</v>
@@ -5504,225 +5687,225 @@
         <v>29</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115" ht="49.7" spans="1:7">
       <c r="A115" s="3">
-        <v>749</v>
+        <v>698</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>272</v>
+        <v>36</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="116" ht="49.7" spans="1:7">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="116" ht="62.15" spans="1:7">
       <c r="A116" s="3">
-        <v>761</v>
+        <v>707</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="117" ht="49.7" spans="1:7">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="117" ht="62.15" spans="1:7">
       <c r="A117" s="3">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="118" ht="62.15" spans="1:7">
       <c r="A118" s="3">
-        <v>787</v>
+        <v>709</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F118" s="5" t="s">
         <v>278</v>
       </c>
+      <c r="F118" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="G118" s="5" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" ht="62.15" spans="1:7">
       <c r="A119" s="3">
-        <v>788</v>
+        <v>710</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="120" ht="74.55" spans="1:7">
       <c r="A120" s="3">
-        <v>789</v>
+        <v>711</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" ht="62.15" spans="1:7">
       <c r="A121" s="3">
-        <v>797</v>
+        <v>712</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>284</v>
+        <v>278</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="122" ht="74.55" spans="1:7">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" ht="62.15" spans="1:7">
       <c r="A122" s="3">
-        <v>798</v>
+        <v>713</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="123" ht="62.15" spans="1:7">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="123" ht="49.7" spans="1:7">
       <c r="A123" s="3">
-        <v>804</v>
+        <v>714</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="124" ht="74.55" spans="1:7">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="124" ht="49.7" spans="1:7">
       <c r="A124" s="3">
-        <v>805</v>
+        <v>749</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>7</v>
@@ -5731,21 +5914,21 @@
         <v>39</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="125" ht="62.15" spans="1:7">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="125" ht="49.7" spans="1:7">
       <c r="A125" s="3">
-        <v>811</v>
+        <v>761</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>7</v>
@@ -5754,21 +5937,21 @@
         <v>39</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="126" ht="74.55" spans="1:7">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="126" ht="49.7" spans="1:7">
       <c r="A126" s="3">
-        <v>812</v>
+        <v>768</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>7</v>
@@ -5777,21 +5960,21 @@
         <v>39</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="127" ht="49.7" spans="1:7">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="127" ht="62.15" spans="1:7">
       <c r="A127" s="3">
-        <v>851</v>
+        <v>787</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>7</v>
@@ -5800,21 +5983,21 @@
         <v>39</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>41</v>
+        <v>295</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>299</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="128" ht="49.7" spans="1:7">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="128" ht="62.15" spans="1:7">
       <c r="A128" s="3">
-        <v>852</v>
+        <v>788</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>7</v>
@@ -5823,21 +6006,21 @@
         <v>39</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>41</v>
+        <v>295</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>299</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="129" ht="49.7" spans="1:7">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="129" ht="74.55" spans="1:7">
       <c r="A129" s="3">
-        <v>853</v>
+        <v>789</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>7</v>
@@ -5846,21 +6029,21 @@
         <v>39</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="130" ht="49.7" spans="1:7">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="130" ht="62.15" spans="1:7">
       <c r="A130" s="3">
-        <v>854</v>
+        <v>797</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>7</v>
@@ -5869,21 +6052,21 @@
         <v>39</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>41</v>
+        <v>295</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>299</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="131" ht="62.15" spans="1:7">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="131" ht="74.55" spans="1:7">
       <c r="A131" s="3">
-        <v>855</v>
+        <v>798</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>7</v>
@@ -5892,21 +6075,21 @@
         <v>39</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="132" ht="49.7" spans="1:7">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="132" ht="62.15" spans="1:7">
       <c r="A132" s="3">
-        <v>856</v>
+        <v>804</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>7</v>
@@ -5915,21 +6098,21 @@
         <v>39</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>306</v>
+        <v>295</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="133" ht="49.7" spans="1:7">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="133" ht="74.55" spans="1:7">
       <c r="A133" s="3">
-        <v>857</v>
+        <v>805</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>7</v>
@@ -5938,21 +6121,21 @@
         <v>39</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>308</v>
+        <v>295</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="134" ht="49.7" spans="1:7">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="134" ht="62.15" spans="1:7">
       <c r="A134" s="3">
-        <v>858</v>
+        <v>811</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>7</v>
@@ -5961,21 +6144,21 @@
         <v>39</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>310</v>
+        <v>295</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>316</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="135" ht="49.7" spans="1:7">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="135" ht="74.55" spans="1:7">
       <c r="A135" s="3">
-        <v>859</v>
+        <v>812</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>7</v>
@@ -5984,2091 +6167,2091 @@
         <v>39</v>
       </c>
       <c r="D135" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="136" ht="49.7" spans="1:7">
+      <c r="A136" s="3">
+        <v>851</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E135" s="8" t="s">
+      <c r="E136" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F135" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="136" ht="62.15" spans="1:7">
-      <c r="A136" s="3">
-        <v>1054</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>316</v>
+      <c r="F136" s="5" t="s">
+        <v>320</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="137" ht="62.15" spans="1:7">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="137" ht="49.7" spans="1:7">
       <c r="A137" s="3">
-        <v>1069</v>
+        <v>852</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>319</v>
+        <v>40</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>322</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="138" ht="62.15" spans="1:7">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="138" ht="49.7" spans="1:7">
       <c r="A138" s="3">
-        <v>1243</v>
+        <v>853</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>323</v>
+        <v>40</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="139" ht="62.15" spans="1:7">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="139" ht="49.7" spans="1:7">
       <c r="A139" s="3">
-        <v>1244</v>
+        <v>854</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>325</v>
+        <v>40</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>326</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="140" ht="62.15" spans="1:7">
       <c r="A140" s="3">
-        <v>1245</v>
+        <v>855</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>327</v>
+        <v>40</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>328</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="141" ht="62.15" spans="1:7">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="141" ht="49.7" spans="1:7">
       <c r="A141" s="3">
-        <v>1246</v>
+        <v>856</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>329</v>
+        <v>40</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>330</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="142" ht="74.55" spans="1:7">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="142" ht="49.7" spans="1:7">
       <c r="A142" s="3">
-        <v>1247</v>
+        <v>857</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>331</v>
+        <v>40</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>332</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="143" ht="62.15" spans="1:7">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="143" ht="49.7" spans="1:7">
       <c r="A143" s="3">
-        <v>1249</v>
+        <v>858</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>333</v>
+        <v>40</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="144" ht="49.7" spans="1:7">
       <c r="A144" s="3">
-        <v>1250</v>
+        <v>859</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>314</v>
+        <v>39</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>335</v>
+        <v>40</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="145" ht="49.7" spans="1:7">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="145" ht="62.15" spans="1:7">
       <c r="A145" s="3">
-        <v>1251</v>
+        <v>1054</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>337</v>
+        <v>10</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="G145" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="146" ht="62.15" spans="1:7">
+      <c r="A146" s="3">
+        <v>1069</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="146" ht="49.7" spans="1:7">
-      <c r="A146" s="3">
-        <v>1252</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>314</v>
-      </c>
       <c r="D146" s="4" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>322</v>
+        <v>10</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="147" ht="62.15" spans="1:7">
       <c r="A147" s="3">
-        <v>1253</v>
+        <v>1243</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="148" ht="62.15" spans="1:7">
       <c r="A148" s="3">
-        <v>1254</v>
+        <v>1244</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="149" ht="62.15" spans="1:7">
       <c r="A149" s="3">
-        <v>1255</v>
+        <v>1245</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" ht="62.15" spans="1:7">
       <c r="A150" s="3">
-        <v>1256</v>
+        <v>1246</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="151" ht="74.55" spans="1:7">
       <c r="A151" s="3">
-        <v>1257</v>
+        <v>1247</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="152" ht="62.15" spans="1:7">
       <c r="A152" s="3">
-        <v>1259</v>
+        <v>1249</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" ht="49.7" spans="1:7">
       <c r="A153" s="3">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="154" ht="49.7" spans="1:7">
       <c r="A154" s="3">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="155" ht="49.7" spans="1:7">
       <c r="A155" s="3">
-        <v>1262</v>
+        <v>1252</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="156" ht="62.15" spans="1:7">
       <c r="A156" s="3">
-        <v>1263</v>
+        <v>1253</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="157" ht="62.15" spans="1:7">
       <c r="A157" s="3">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="158" ht="62.15" spans="1:7">
       <c r="A158" s="3">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="159" ht="62.15" spans="1:7">
       <c r="A159" s="3">
-        <v>1266</v>
+        <v>1256</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="160" ht="62.15" spans="1:7">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="160" ht="74.55" spans="1:7">
       <c r="A160" s="3">
-        <v>1267</v>
+        <v>1257</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="161" ht="62.15" spans="1:7">
       <c r="A161" s="3">
-        <v>1268</v>
+        <v>1259</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="162" ht="74.55" spans="1:7">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="162" ht="49.7" spans="1:7">
       <c r="A162" s="3">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="163" ht="74.55" spans="1:7">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="163" ht="49.7" spans="1:7">
       <c r="A163" s="3">
-        <v>1270</v>
+        <v>1261</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>373</v>
+        <v>346</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>379</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="164" ht="62.15" spans="1:7">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="164" ht="49.7" spans="1:7">
       <c r="A164" s="3">
-        <v>1272</v>
+        <v>1262</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="165" ht="62.15" spans="1:7">
       <c r="A165" s="3">
-        <v>1273</v>
+        <v>1263</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" ht="62.15" spans="1:7">
       <c r="A166" s="3">
-        <v>1274</v>
+        <v>1264</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" ht="62.15" spans="1:7">
       <c r="A167" s="3">
-        <v>1275</v>
+        <v>1265</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="168" ht="62.15" spans="1:7">
       <c r="A168" s="3">
-        <v>1276</v>
+        <v>1266</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="169" ht="62.15" spans="1:7">
       <c r="A169" s="3">
-        <v>1277</v>
+        <v>1267</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="170" ht="62.15" spans="1:7">
       <c r="A170" s="3">
-        <v>1278</v>
+        <v>1268</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="171" ht="74.55" spans="1:7">
       <c r="A171" s="3">
-        <v>1279</v>
+        <v>1269</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="172" ht="74.55" spans="1:7">
       <c r="A172" s="3">
-        <v>1280</v>
+        <v>1270</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="173" ht="62.15" spans="1:7">
       <c r="A173" s="3">
-        <v>1281</v>
+        <v>1272</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="174" ht="62.15" spans="1:7">
       <c r="A174" s="3">
-        <v>1282</v>
+        <v>1273</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="175" ht="62.15" spans="1:7">
       <c r="A175" s="3">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="176" ht="62.15" spans="1:7">
       <c r="A176" s="3">
-        <v>1284</v>
+        <v>1275</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="177" ht="62.15" spans="1:7">
       <c r="A177" s="3">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="178" ht="74.55" spans="1:7">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="178" ht="62.15" spans="1:7">
       <c r="A178" s="3">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="179" ht="74.55" spans="1:7">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="179" ht="62.15" spans="1:7">
       <c r="A179" s="3">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="180" ht="62.15" spans="1:7">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="180" ht="74.55" spans="1:7">
       <c r="A180" s="3">
-        <v>1288</v>
+        <v>1279</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="181" ht="62.15" spans="1:7">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="181" ht="74.55" spans="1:7">
       <c r="A181" s="3">
-        <v>1289</v>
+        <v>1280</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="182" ht="62.15" spans="1:7">
       <c r="A182" s="3">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="183" ht="74.55" spans="1:7">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="183" ht="62.15" spans="1:7">
       <c r="A183" s="3">
-        <v>1294</v>
+        <v>1282</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="184" ht="62.15" spans="1:7">
       <c r="A184" s="3">
-        <v>1297</v>
+        <v>1283</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" ht="62.15" spans="1:7">
       <c r="A185" s="3">
-        <v>1298</v>
+        <v>1284</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" ht="62.15" spans="1:7">
       <c r="A186" s="3">
-        <v>1299</v>
+        <v>1285</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" ht="74.55" spans="1:7">
       <c r="A187" s="3">
-        <v>1300</v>
+        <v>1286</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" ht="74.55" spans="1:7">
       <c r="A188" s="3">
-        <v>1301</v>
+        <v>1287</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" ht="62.15" spans="1:7">
       <c r="A189" s="3">
-        <v>1302</v>
+        <v>1288</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" ht="62.15" spans="1:7">
       <c r="A190" s="3">
-        <v>1303</v>
+        <v>1289</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" ht="62.15" spans="1:7">
       <c r="A191" s="3">
-        <v>1307</v>
+        <v>1293</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="192" ht="49.7" spans="1:7">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="192" ht="74.55" spans="1:7">
       <c r="A192" s="3">
-        <v>1313</v>
+        <v>1294</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="193" ht="49.7" spans="1:7">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="193" ht="62.15" spans="1:7">
       <c r="A193" s="3">
-        <v>1317</v>
+        <v>1297</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>45</v>
+        <v>440</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="194" ht="49.7" spans="1:7">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="194" ht="62.15" spans="1:7">
       <c r="A194" s="3">
-        <v>1318</v>
+        <v>1298</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>45</v>
+        <v>440</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="195" ht="49.7" spans="1:7">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="195" ht="62.15" spans="1:7">
       <c r="A195" s="3">
-        <v>1319</v>
+        <v>1299</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>45</v>
+        <v>440</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F195" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="196" ht="74.55" spans="1:7">
+      <c r="A196" s="3">
+        <v>1300</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D196" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="196" ht="62.15" spans="1:7">
-      <c r="A196" s="3">
-        <v>1320</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D196" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="197" ht="49.7" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="197" ht="74.55" spans="1:7">
       <c r="A197" s="3">
-        <v>1321</v>
+        <v>1301</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>45</v>
+        <v>440</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="198" ht="49.7" spans="1:7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="198" ht="62.15" spans="1:7">
       <c r="A198" s="3">
+        <v>1302</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="199" ht="62.15" spans="1:7">
+      <c r="A199" s="3">
+        <v>1303</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="200" ht="62.15" spans="1:7">
+      <c r="A200" s="3">
+        <v>1307</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G200" s="5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="201" ht="49.7" spans="1:7">
+      <c r="A201" s="3">
+        <v>1313</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="202" ht="49.7" spans="1:7">
+      <c r="A202" s="3">
+        <v>1317</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="203" ht="49.7" spans="1:7">
+      <c r="A203" s="3">
+        <v>1318</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="204" ht="49.7" spans="1:7">
+      <c r="A204" s="3">
+        <v>1319</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G204" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="205" ht="62.15" spans="1:7">
+      <c r="A205" s="3">
+        <v>1320</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="206" ht="49.7" spans="1:7">
+      <c r="A206" s="3">
+        <v>1321</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G206" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="207" ht="49.7" spans="1:7">
+      <c r="A207" s="3">
         <v>2144</v>
       </c>
-      <c r="B198" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G198" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="199" ht="74.55" spans="1:7">
-      <c r="A199" s="3">
-        <v>2250</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D199" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E199" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F199" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="G199" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="200" ht="74.55" spans="1:7">
-      <c r="A200" s="3">
-        <v>2251</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D200" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F200" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="G200" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="201" ht="74.55" spans="1:7">
-      <c r="A201" s="3">
-        <v>2252</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D201" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E201" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F201" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="G201" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="202" ht="74.55" spans="1:7">
-      <c r="A202" s="3">
-        <v>2253</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D202" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E202" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F202" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="G202" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="203" ht="87" spans="1:7">
-      <c r="A203" s="3">
-        <v>2254</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D203" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E203" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="G203" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="204" ht="87" spans="1:7">
-      <c r="A204" s="3">
-        <v>2255</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D204" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E204" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="G204" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="205" ht="87" spans="1:7">
-      <c r="A205" s="3">
-        <v>2256</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D205" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E205" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="G205" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="206" ht="87" spans="1:7">
-      <c r="A206" s="3">
-        <v>2257</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E206" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="G206" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="207" ht="74.55" spans="1:7">
-      <c r="A207" s="3">
-        <v>2258</v>
-      </c>
       <c r="B207" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>451</v>
+        <v>49</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F207" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>471</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="208" ht="74.55" spans="1:7">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="208" ht="49.7" spans="1:7">
       <c r="A208" s="3">
-        <v>2259</v>
+        <v>2152</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>451</v>
+        <v>49</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>50</v>
+        <v>473</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="209" ht="74.55" spans="1:7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="209" ht="62.15" spans="1:7">
       <c r="A209" s="3">
-        <v>2260</v>
+        <v>2155</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>451</v>
+        <v>49</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F209" s="7" t="s">
-        <v>472</v>
+      <c r="F209" s="5" t="s">
+        <v>476</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="210" ht="74.55" spans="1:7">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="210" ht="62.15" spans="1:7">
       <c r="A210" s="3">
-        <v>2261</v>
+        <v>2156</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>451</v>
+        <v>49</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F210" s="7" t="s">
-        <v>474</v>
+      <c r="F210" s="5" t="s">
+        <v>478</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" ht="62.15" spans="1:7">
       <c r="A211" s="3">
-        <v>2270</v>
+        <v>2157</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F211" s="7" t="s">
-        <v>477</v>
+      <c r="F211" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" ht="62.15" spans="1:7">
       <c r="A212" s="3">
-        <v>2271</v>
+        <v>2158</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F212" s="7" t="s">
-        <v>479</v>
+      <c r="F212" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="213" ht="62.15" spans="1:7">
       <c r="A213" s="3">
-        <v>2272</v>
+        <v>2159</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F213" s="7" t="s">
-        <v>481</v>
+      <c r="F213" s="5" t="s">
+        <v>484</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="214" ht="62.15" spans="1:7">
       <c r="A214" s="3">
-        <v>2273</v>
+        <v>2165</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="215" ht="62.15" spans="1:7">
       <c r="A215" s="3">
-        <v>2274</v>
+        <v>2166</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="216" ht="62.15" spans="1:7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="216" ht="74.55" spans="1:7">
       <c r="A216" s="3">
-        <v>2275</v>
+        <v>2167</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="217" ht="62.15" spans="1:7">
       <c r="A217" s="3">
-        <v>2276</v>
+        <v>2168</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="218" ht="62.15" spans="1:7">
       <c r="A218" s="3">
-        <v>2277</v>
+        <v>2169</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="219" ht="62.15" spans="1:7">
       <c r="A219" s="3">
-        <v>2278</v>
+        <v>2170</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="220" ht="62.15" spans="1:7">
       <c r="A220" s="3">
-        <v>2279</v>
+        <v>2171</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="221" ht="62.15" spans="1:7">
       <c r="A221" s="3">
-        <v>2280</v>
+        <v>2172</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="222" ht="62.15" spans="1:7">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="222" ht="49.7" spans="1:7">
       <c r="A222" s="3">
-        <v>2281</v>
+        <v>2193</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>50</v>
+        <v>503</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>491</v>
+        <v>177</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="223" ht="62.15" spans="1:7">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="223" ht="49.7" spans="1:7">
       <c r="A223" s="3">
-        <v>2310</v>
+        <v>2194</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>50</v>
+        <v>503</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>496</v>
+        <v>179</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="224" ht="62.15" spans="1:7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="224" ht="49.7" spans="1:7">
       <c r="A224" s="3">
-        <v>2311</v>
+        <v>2196</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>50</v>
+        <v>503</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G224" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="225" ht="62.15" spans="1:7">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="225" ht="74.55" spans="1:7">
       <c r="A225" s="3">
-        <v>2312</v>
+        <v>2250</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>446</v>
+        <v>48</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>495</v>
+        <v>56</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="226" ht="62.15" spans="1:7">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="226" ht="74.55" spans="1:7">
       <c r="A226" s="3">
-        <v>2575</v>
+        <v>2251</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>7</v>
@@ -8077,19 +8260,21 @@
         <v>48</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="E226" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="F226" s="7" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="227" ht="62.15" spans="1:7">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="227" ht="74.55" spans="1:7">
       <c r="A227" s="3">
-        <v>2592</v>
+        <v>2252</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>7</v>
@@ -8098,21 +8283,21 @@
         <v>48</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>505</v>
+        <v>56</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="228" ht="62.15" spans="1:7">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="228" ht="74.55" spans="1:7">
       <c r="A228" s="3">
-        <v>2603</v>
+        <v>2253</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>7</v>
@@ -8121,21 +8306,21 @@
         <v>48</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>508</v>
+        <v>56</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="229" ht="62.15" spans="1:7">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="229" ht="87" spans="1:7">
       <c r="A229" s="3">
-        <v>2606</v>
+        <v>2254</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>7</v>
@@ -8144,21 +8329,21 @@
         <v>48</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="230" ht="62.15" spans="1:7">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="230" ht="87" spans="1:7">
       <c r="A230" s="3">
-        <v>2607</v>
+        <v>2255</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>7</v>
@@ -8167,21 +8352,21 @@
         <v>48</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="231" ht="62.15" spans="1:7">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="231" ht="87" spans="1:7">
       <c r="A231" s="3">
-        <v>2608</v>
+        <v>2256</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>7</v>
@@ -8190,21 +8375,21 @@
         <v>48</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F231" s="7" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="232" ht="49.7" spans="1:7">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="232" ht="87" spans="1:7">
       <c r="A232" s="3">
-        <v>2609</v>
+        <v>2257</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>7</v>
@@ -8213,21 +8398,21 @@
         <v>48</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="233" ht="49.7" spans="1:7">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="233" ht="74.55" spans="1:7">
       <c r="A233" s="3">
-        <v>2610</v>
+        <v>2258</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>7</v>
@@ -8236,21 +8421,21 @@
         <v>48</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="234" ht="49.7" spans="1:7">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="234" ht="74.55" spans="1:7">
       <c r="A234" s="3">
-        <v>2611</v>
+        <v>2259</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>7</v>
@@ -8259,21 +8444,21 @@
         <v>48</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="235" ht="49.7" spans="1:7">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="235" ht="74.55" spans="1:7">
       <c r="A235" s="3">
-        <v>2612</v>
+        <v>2260</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>7</v>
@@ -8282,21 +8467,21 @@
         <v>48</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="236" ht="49.7" spans="1:7">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="236" ht="74.55" spans="1:7">
       <c r="A236" s="3">
-        <v>2613</v>
+        <v>2261</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>7</v>
@@ -8305,21 +8490,21 @@
         <v>48</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="237" ht="62.15" spans="1:7">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="237" ht="49.7" spans="1:7">
       <c r="A237" s="3">
-        <v>2614</v>
+        <v>2266</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>7</v>
@@ -8328,21 +8513,21 @@
         <v>48</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="238" ht="62.15" spans="1:7">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="238" ht="49.7" spans="1:7">
       <c r="A238" s="3">
-        <v>2615</v>
+        <v>2267</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>7</v>
@@ -8351,21 +8536,21 @@
         <v>48</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="239" ht="62.15" spans="1:7">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="239" ht="49.7" spans="1:7">
       <c r="A239" s="3">
-        <v>2616</v>
+        <v>2268</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>7</v>
@@ -8374,21 +8559,21 @@
         <v>48</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="240" ht="62.15" spans="1:7">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="240" ht="49.7" spans="1:7">
       <c r="A240" s="3">
-        <v>2617</v>
+        <v>2269</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>7</v>
@@ -8397,16 +8582,704 @@
         <v>48</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="241" ht="62.15" spans="1:7">
+      <c r="A241" s="3">
+        <v>2270</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="242" ht="62.15" spans="1:7">
+      <c r="A242" s="3">
+        <v>2271</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E242" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F242" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="243" ht="62.15" spans="1:7">
+      <c r="A243" s="3">
+        <v>2272</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E243" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F243" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="244" ht="62.15" spans="1:7">
+      <c r="A244" s="3">
+        <v>2273</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E244" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F244" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="245" ht="62.15" spans="1:7">
+      <c r="A245" s="3">
+        <v>2274</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E245" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="246" ht="62.15" spans="1:7">
+      <c r="A246" s="3">
+        <v>2275</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E246" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G246" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="247" ht="62.15" spans="1:7">
+      <c r="A247" s="3">
+        <v>2276</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="248" ht="62.15" spans="1:7">
+      <c r="A248" s="3">
+        <v>2277</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="G248" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="249" ht="62.15" spans="1:7">
+      <c r="A249" s="3">
+        <v>2278</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E249" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F249" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="250" ht="62.15" spans="1:7">
+      <c r="A250" s="3">
+        <v>2279</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E250" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G250" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="251" ht="62.15" spans="1:7">
+      <c r="A251" s="3">
+        <v>2280</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F251" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="252" ht="62.15" spans="1:7">
+      <c r="A252" s="3">
+        <v>2281</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="G252" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="253" ht="62.15" spans="1:7">
+      <c r="A253" s="3">
+        <v>2310</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="G253" s="5" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="254" ht="62.15" spans="1:7">
+      <c r="A254" s="3">
+        <v>2311</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="G254" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="255" ht="62.15" spans="1:7">
+      <c r="A255" s="3">
+        <v>2312</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E255" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="G255" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="256" ht="62.15" spans="1:7">
+      <c r="A256" s="3">
+        <v>2575</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E256" s="4"/>
+      <c r="F256" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="G256" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="257" ht="62.15" spans="1:7">
+      <c r="A257" s="3">
+        <v>2592</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="G257" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="258" ht="62.15" spans="1:7">
+      <c r="A258" s="3">
+        <v>2603</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="G258" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="259" ht="62.15" spans="1:7">
+      <c r="A259" s="3">
+        <v>2606</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="G259" s="5" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="260" ht="62.15" spans="1:7">
+      <c r="A260" s="3">
+        <v>2607</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="G260" s="5" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="261" ht="62.15" spans="1:7">
+      <c r="A261" s="3">
+        <v>2608</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F261" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="G261" s="5" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="262" ht="49.7" spans="1:7">
+      <c r="A262" s="3">
+        <v>2609</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F262" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="G262" s="5" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="263" ht="49.7" spans="1:7">
+      <c r="A263" s="3">
+        <v>2610</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E263" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F263" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="G263" s="5" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="264" ht="49.7" spans="1:7">
+      <c r="A264" s="3">
+        <v>2611</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E264" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F264" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="G264" s="5" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="265" ht="49.7" spans="1:7">
+      <c r="A265" s="3">
+        <v>2612</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E265" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F265" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="G265" s="5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="266" ht="49.7" spans="1:7">
+      <c r="A266" s="3">
+        <v>2613</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="G266" s="5" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="267" ht="62.15" spans="1:7">
+      <c r="A267" s="3">
+        <v>2614</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E267" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="G267" s="5" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="268" ht="62.15" spans="1:7">
+      <c r="A268" s="3">
+        <v>2615</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F268" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="269" ht="62.15" spans="1:7">
+      <c r="A269" s="3">
+        <v>2616</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E269" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F269" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="270" ht="62.15" spans="1:7">
+      <c r="A270" s="3">
+        <v>2617</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E270" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F270" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="G270" s="5" t="s">
+        <v>595</v>
       </c>
     </row>
   </sheetData>
